--- a/doc/001_OpenVLSI_Resource.xlsx
+++ b/doc/001_OpenVLSI_Resource.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="30029"/>
-  <workbookPr defaultThemeVersion="202300"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="27328"/>
+  <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\002_GitHub\VLSIT_SOC_Starter\doc\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\Git\VLSIT_SOC_Starter\doc\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="8_{90881FE0-3A9E-4DB1-8442-7ECC3F60DBAD}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{2586FFDB-FD4E-4E27-A962-1669B11CDB15}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-110" yWindow="-110" windowWidth="19420" windowHeight="11500" activeTab="1" xr2:uid="{B6857A90-25D4-4A67-8903-7C0067D27823}"/>
+    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="13896" activeTab="1" xr2:uid="{B6857A90-25D4-4A67-8903-7C0067D27823}"/>
   </bookViews>
   <sheets>
     <sheet name="Rev. History" sheetId="2" r:id="rId1"/>
@@ -28,7 +28,6 @@
         <xcalcf:feature name="microsoft.com:FV"/>
         <xcalcf:feature name="microsoft.com:CNMTM"/>
         <xcalcf:feature name="microsoft.com:LET_WF"/>
-        <xcalcf:feature name="microsoft.com:LAMBDA_WF"/>
         <xcalcf:feature name="microsoft.com:ARRAYTEXT_WF"/>
       </xcalcf:calcFeatures>
     </ext>
@@ -37,7 +36,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="35" uniqueCount="34">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="93" uniqueCount="91">
   <si>
     <t>No.</t>
   </si>
@@ -72,27 +71,9 @@
     <t>I2C</t>
   </si>
   <si>
-    <t>I3C</t>
-  </si>
-  <si>
-    <t>GPIO</t>
-  </si>
-  <si>
-    <t>Timer</t>
-  </si>
-  <si>
     <t>WDT</t>
   </si>
   <si>
-    <t>LIN</t>
-  </si>
-  <si>
-    <t>CAN</t>
-  </si>
-  <si>
-    <t>USB</t>
-  </si>
-  <si>
     <t>Person</t>
   </si>
   <si>
@@ -139,13 +120,438 @@
   </si>
   <si>
     <t>AHB2APB</t>
+  </si>
+  <si>
+    <t>BUG #1 — ARREADY/AWREADY handshake không chuẩn AXI
+Đây là vấn đề lớn nhất.
+Ví dụ:
+when READ_ADDRESS_RECEIVED_STATE =&gt;
+    S_AXI_ARREADY &lt;= '1';
+Nghĩa là:
+READY chỉ assert SAU khi FSM đã chuyển state.
+Nhưng state transition lại dùng:
+if (S_AXI_ARVALID = '1')
+từ IDLE.
+=&gt; handshake thực sự:
+VALID=1
+READY=0
+ở cycle detect.
+READY chỉ lên:
+cycle sau.
+Điều này không sai hoàn toàn,
+NHƯNG:
+không phải canonical AXI handshake style
+và dễ gây corner-case issue.</t>
+  </si>
+  <si>
+    <t>9. Design đang assume VALID giữ stable
+AXI spec cho phép:
+VALID phải giữ cho tới READY.
+Nên technically:
+vẫn hoạt động.
+Nhưng industrial design thường:
+READY combinationally visible
+hoặc:
+skid-buffered.</t>
+  </si>
+  <si>
+    <t>BUG #2 — AW và W synchronization còn yếu
+AXI-Lite cho phép:
+AWVALID và WVALID đến lệch nhau rất xa
+Design này:
+WRITE_ADDRESS_RECEIVED_STATE
+đợi WVALID.
+OK.
+Nhưng:
+chỉ support single in-flight write cực cứng
+không có buffering.
+=&gt; throughput thấp nhưng functional OK.</t>
+  </si>
+  <si>
+    <t>BUG #3 — sampled_wdata logic hơi nguy hiểm
+Đoạn:
+elsif(present_state = WDATA_TRANSFERRED_STATE and S_AXI_WVALID = '1')
+rất đáng nghi.
+Tại sao còn sample WDATA ở:
+WDATA_TRANSFERRED_STATE
+?
+Lúc này transaction đã gần xong.
+Có thể:
+vô tình accept write mới quá sớm.
+Đây có khả năng bug hidden.</t>
+  </si>
+  <si>
+    <t>BUG #4 — RDATA bị clear quá aggressive
+Đây là subtle bug.
+else
+    S_AXI_RDATA &lt;= (others =&gt; '0');
+Nghĩa là:
+nếu không đúng condition
+RDATA bị zero liên tục.
+Trong AXI:
+RDATA phải stable khi RVALID=1 cho tới handshake
+Design này MAY still work vì:
+state machine giữ RVALID.
+Nhưng:
+style này nguy hiểm.
+Industrial style thường:
+hold-last-value</t>
+  </si>
+  <si>
+    <t>BUG #5 — BRESP/RRESP không hold rõ ràng
+Ví dụ:
+if(condition)
+   BRESP &lt;= ...
+Không có explicit:
+hold state.
+Có thể synthesis OK,
+nhưng readability và robustness chưa đẹp.</t>
+  </si>
+  <si>
+    <t>https://github.com/mahmutefil/AXI2APB-Bridge-Design-and-Verification
+Last update Updated on 17 thg 7, 2014</t>
+  </si>
+  <si>
+    <t>Support AXI feature beyond AXI-Lite (Support write strobe/ BRUST transaction -(exsits AWLEN / ARLEN/ WLAST)
+Support converts bitwidth 
+ Exsist Internal buffer (APB latency handling/ Reduce the dependence between AXI and APB.)</t>
+  </si>
+  <si>
+    <r>
+      <t xml:space="preserve">Support AXI Lite /APB3 interface
+Single outstanding 
+Synchrous clock (only one clock domain)
+Read more priority than Write (FSM processes AXI read before AXI write to transfer to APB)
+Error translation mechanism (PSLVERR --&gt; SLVERR)
+</t>
+    </r>
+    <r>
+      <rPr>
+        <u/>
+        <sz val="13"/>
+        <color theme="1"/>
+        <rFont val="Arial"/>
+        <family val="2"/>
+      </rPr>
+      <t>Note:</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="13"/>
+        <color theme="1"/>
+        <rFont val="Arial"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">
+Han: When PSLVERR  = 1 --&gt; SLVERR = 10
+Design: When SSLVERR =1 --&gt; SLVERR = 11
+accroding AXI standard 
+when SLVERR
+00       OKAY
+10       SLVERR --&gt; Slave exsits but operation fail: protection violation/ unsupported access/ periheral error
+11       DECERR  --&gt; Decode error --&gt; Không tìm thấy slave có address đó 
+The APB3 doesn't support "Decode Error"
+According to APB3 spec: "“PSLVERR is only considered valid during the last cycle of an APB transfer, when PSEL, PENABLE, and PREADY are all HIGH." The PREADY is HIGH means the Slave exists
+</t>
+    </r>
+    <r>
+      <rPr>
+        <i/>
+        <sz val="13"/>
+        <color theme="1"/>
+        <rFont val="Arial"/>
+        <family val="2"/>
+      </rPr>
+      <t>This point is different from the APB Bridge LogiCORE IP Product Guide mentioned in the README.</t>
+    </r>
+  </si>
+  <si>
+    <t>https://github.com/YosysHQ/picorv32.git</t>
+  </si>
+  <si>
+    <t>https://github.com/ultraembedded/riscv.git</t>
+  </si>
+  <si>
+    <t>https://github.com/SpinalHDL/VexRiscv.git</t>
+  </si>
+  <si>
+    <t>AXI</t>
+  </si>
+  <si>
+    <t>https://github.com/ZipCPU/wb2axip/blob/master/README.md</t>
+  </si>
+  <si>
+    <t>https://github.com/funningboy/uvm_axi.git</t>
+  </si>
+  <si>
+    <t>https://github.com/Architech-Silica/Designing-a-Custom-AXI-Master-using-BFMs.git</t>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="13"/>
+        <color theme="1"/>
+        <rFont val="Arial"/>
+        <family val="2"/>
+      </rPr>
+      <t>Initial guess:</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="13"/>
+        <color theme="1"/>
+        <rFont val="Arial"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">
+Last updated 2013 --&gt; It may become outdated.
+Maybe AXI3 (WID exsits)</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="13"/>
+        <color theme="1"/>
+        <rFont val="Arial"/>
+        <family val="2"/>
+      </rPr>
+      <t>Initial guess:</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="13"/>
+        <color theme="1"/>
+        <rFont val="Arial"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">
+Maybe AXI3 (WID exsits)
+AXI master only </t>
+    </r>
+  </si>
+  <si>
+    <t>AHB</t>
+  </si>
+  <si>
+    <t>https://github.com/lucky-wfw/ARM_AMBA_Design.git</t>
+  </si>
+  <si>
+    <r>
+      <t xml:space="preserve">Initial guess:
+</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="13"/>
+        <color theme="1"/>
+        <rFont val="Arial"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">Include slave and master
+AHB-Lite/AHB4 simplified (however the repo include AHB5 spec)
+</t>
+    </r>
+  </si>
+  <si>
+    <t>https://github.com/Lianghao-Yuan/AHB_Bus_Matrix.git</t>
+  </si>
+  <si>
+    <t>https://github.com/Buddhimah/System-Bus-Design-Verilog.git</t>
+  </si>
+  <si>
+    <r>
+      <t xml:space="preserve">No Readme
+</t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="13"/>
+        <color theme="1"/>
+        <rFont val="Arial"/>
+        <family val="2"/>
+      </rPr>
+      <t>Initial guess</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="13"/>
+        <color theme="1"/>
+        <rFont val="Arial"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">
+AHB subsystem (include bus matrix + arbiter + decoder)/ Multi master
+</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="13"/>
+        <color theme="1"/>
+        <rFont val="Arial"/>
+        <family val="2"/>
+      </rPr>
+      <t>Initial guess:</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="13"/>
+        <color theme="1"/>
+        <rFont val="Arial"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">
+Multi master Multi slave system </t>
+    </r>
+  </si>
+  <si>
+    <t>APB</t>
+  </si>
+  <si>
+    <t>https://github.com/MuddasirAttar/APB-Master-Slave.git</t>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="13"/>
+        <color theme="1"/>
+        <rFont val="Arial"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">
+</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="13"/>
+        <color theme="1"/>
+        <rFont val="Arial"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">APB3
+include master and slave </t>
+    </r>
+  </si>
+  <si>
+    <t>https://github.com/PavanSC/APB-Protocol-Design-and-verification.git</t>
+  </si>
+  <si>
+    <t>https://github.com/moonishav1997/ambabridge.git</t>
+  </si>
+  <si>
+    <t>https://github.com/pranav-nb/APB_BFM.git</t>
+  </si>
+  <si>
+    <t>Testbench and design are combined into one file.</t>
+  </si>
+  <si>
+    <t>https://github.com/KasuganoSoraaa/simple-AXI2AHB-bridge.git</t>
+  </si>
+  <si>
+    <t>https://github.com/freecores/robust_axi2ahb.git</t>
+  </si>
+  <si>
+    <t>https://github.com/forrest3444/AXI2AHB-Lite-Bridge-UVM-Verification.git</t>
+  </si>
+  <si>
+    <t>https://github.com/Germanyy0410/AHB2AXI4.git</t>
+  </si>
+  <si>
+    <t>https://github.com/AccurateRTL/lio_ahb2axi.git</t>
+  </si>
+  <si>
+    <t>https://github.com/prajwalgekkouga/AHB-to-APB-Bridge.git</t>
+  </si>
+  <si>
+    <t>https://github.com/Siddhi-95/AHB-to-APB-Bridge-Verification.git</t>
+  </si>
+  <si>
+    <t>https://github.com/designsolver/ahb2apb_bridge_vip.git</t>
+  </si>
+  <si>
+    <t>https://github.com/gvsrmk/Design-and-Verification-of-DDR3-SDRAM-memory-controller.git</t>
+  </si>
+  <si>
+    <t>https://github.com/antmicro/lpddr4-dram-controller-integration-soc.git</t>
+  </si>
+  <si>
+    <t>https://github.com/srishis/DMA8237A.git</t>
+  </si>
+  <si>
+    <t>https://github.com/jjtmx/zynq-dma.git</t>
+  </si>
+  <si>
+    <t>https://github.com/muhammedkamal/DMA-.git</t>
+  </si>
+  <si>
+    <t>https://github.com/pConst/basic_verilog.git</t>
+  </si>
+  <si>
+    <t>https://github.com/ultraembedded/cores.git</t>
+  </si>
+  <si>
+    <t>https://github.com/alexforencich/verilog-uart.git</t>
+  </si>
+  <si>
+    <t>https://github.com/ilyajob05/verilog_modules.git</t>
+  </si>
+  <si>
+    <t>https://github.com/AkshayXPatil/Physical-Layout-Design.git</t>
+  </si>
+  <si>
+    <t>https://github.com/Sarafim/USART.git</t>
+  </si>
+  <si>
+    <t>https://github.com/janschiefer/verilog_spi.git</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://github.com/nandland/spi-master.git
+https://github.com/nandland/spi-slave.git
+</t>
+  </si>
+  <si>
+    <t>https://github.com/sergachev/spi_mem_programmer.git</t>
+  </si>
+  <si>
+    <t>https://github.com/dineshannayya/qspis.git</t>
+  </si>
+  <si>
+    <t>https://github.com/caicaicai-ji/QSPI_FOR_SOC.git</t>
+  </si>
+  <si>
+    <t>https://github.com/dineshannayya/yifive_r0.git</t>
+  </si>
+  <si>
+    <t>https://github.com/alexforencich/verilog-i2c.git</t>
+  </si>
+  <si>
+    <t>https://github.com/hdl-util/i2c.git</t>
+  </si>
+  <si>
+    <t>https://github.com/freecores/i2c.git</t>
+  </si>
+  <si>
+    <t>https://github.com/peruraj/verilog.git</t>
+  </si>
+  <si>
+    <t>https://github.com/freecores/watchdog.git</t>
+  </si>
+  <si>
+    <t>https://github.com/nguyenhong-hoa/WatchdogTimer.git</t>
   </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
-  <fonts count="5" x14ac:knownFonts="1">
+  <fonts count="7" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -176,6 +582,20 @@
     </font>
     <font>
       <b/>
+      <sz val="13"/>
+      <color theme="1"/>
+      <name val="Arial"/>
+      <family val="2"/>
+    </font>
+    <font>
+      <u/>
+      <sz val="13"/>
+      <color theme="1"/>
+      <name val="Arial"/>
+      <family val="2"/>
+    </font>
+    <font>
+      <i/>
       <sz val="13"/>
       <color theme="1"/>
       <name val="Arial"/>
@@ -218,7 +638,7 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
   </cellStyleXfs>
-  <cellXfs count="7">
+  <cellXfs count="12">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="center"/>
@@ -237,6 +657,21 @@
     </xf>
     <xf numFmtId="0" fontId="4" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="1" xfId="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="1" xfId="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="1" applyAlignment="1">
+      <alignment vertical="center"/>
     </xf>
   </cellXfs>
   <cellStyles count="2">
@@ -574,42 +1009,42 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{8277DC2E-8104-442A-B03F-00979FFE7A07}">
   <dimension ref="A2:C5"/>
-  <sheetFormatPr defaultRowHeight="16.5" x14ac:dyDescent="0.35"/>
+  <sheetFormatPr defaultColWidth="8.77734375" defaultRowHeight="16.8" x14ac:dyDescent="0.3"/>
   <cols>
-    <col min="1" max="1" width="4.6328125" style="2" bestFit="1" customWidth="1"/>
-    <col min="2" max="2" width="15.36328125" style="2" bestFit="1" customWidth="1"/>
-    <col min="3" max="3" width="47.1796875" style="2" customWidth="1"/>
-    <col min="4" max="16384" width="8.7265625" style="2"/>
+    <col min="1" max="1" width="4.6640625" style="2" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="15.33203125" style="2" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="47.21875" style="2" customWidth="1"/>
+    <col min="4" max="16384" width="8.77734375" style="2"/>
   </cols>
   <sheetData>
-    <row r="2" spans="1:3" x14ac:dyDescent="0.35">
+    <row r="2" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A2" s="5" t="s">
         <v>0</v>
       </c>
       <c r="B2" s="5" t="s">
-        <v>18</v>
+        <v>12</v>
       </c>
       <c r="C2" s="5" t="s">
         <v>4</v>
       </c>
     </row>
-    <row r="3" spans="1:3" x14ac:dyDescent="0.35">
+    <row r="3" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A3" s="1">
         <v>1</v>
       </c>
       <c r="B3" s="1" t="s">
-        <v>19</v>
+        <v>13</v>
       </c>
       <c r="C3" s="1" t="s">
-        <v>20</v>
-      </c>
-    </row>
-    <row r="4" spans="1:3" x14ac:dyDescent="0.35">
+        <v>14</v>
+      </c>
+    </row>
+    <row r="4" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A4" s="1"/>
       <c r="B4" s="1"/>
       <c r="C4" s="1"/>
     </row>
-    <row r="5" spans="1:3" x14ac:dyDescent="0.35">
+    <row r="5" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A5" s="1"/>
       <c r="B5" s="1"/>
       <c r="C5" s="1"/>
@@ -621,19 +1056,24 @@
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{53B9D3ED-3076-4299-B077-6E810E94CF83}">
-  <dimension ref="A2:F23"/>
-  <sheetFormatPr defaultRowHeight="16.5" x14ac:dyDescent="0.35"/>
+  <dimension ref="A2:L67"/>
+  <sheetFormatPr defaultColWidth="8.77734375" defaultRowHeight="16.8" x14ac:dyDescent="0.3"/>
   <cols>
-    <col min="1" max="1" width="4.36328125" style="2" bestFit="1" customWidth="1"/>
-    <col min="2" max="2" width="18.90625" style="2" bestFit="1" customWidth="1"/>
-    <col min="3" max="3" width="28.1796875" style="2" bestFit="1" customWidth="1"/>
-    <col min="4" max="4" width="5.90625" style="2" bestFit="1" customWidth="1"/>
-    <col min="5" max="5" width="16.54296875" style="2" bestFit="1" customWidth="1"/>
-    <col min="6" max="6" width="83.26953125" style="2" customWidth="1"/>
-    <col min="7" max="16384" width="8.7265625" style="2"/>
+    <col min="1" max="1" width="4.33203125" style="2" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="18.88671875" style="2" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="37.21875" style="2" customWidth="1"/>
+    <col min="4" max="4" width="78.21875" style="2" customWidth="1"/>
+    <col min="5" max="5" width="16.5546875" style="2" bestFit="1" customWidth="1"/>
+    <col min="6" max="6" width="83.21875" style="2" customWidth="1"/>
+    <col min="7" max="7" width="54.21875" style="2" customWidth="1"/>
+    <col min="8" max="8" width="39" style="2" customWidth="1"/>
+    <col min="9" max="9" width="54.77734375" style="2" customWidth="1"/>
+    <col min="10" max="10" width="49.109375" style="2" customWidth="1"/>
+    <col min="11" max="11" width="17.5546875" style="2" customWidth="1"/>
+    <col min="12" max="16384" width="8.77734375" style="2"/>
   </cols>
   <sheetData>
-    <row r="2" spans="1:6" s="6" customFormat="1" x14ac:dyDescent="0.35">
+    <row r="2" spans="1:6" s="6" customFormat="1" x14ac:dyDescent="0.3">
       <c r="A2" s="5" t="s">
         <v>0</v>
       </c>
@@ -641,19 +1081,19 @@
         <v>1</v>
       </c>
       <c r="C2" s="5" t="s">
-        <v>21</v>
+        <v>15</v>
       </c>
       <c r="D2" s="5" t="s">
         <v>3</v>
       </c>
       <c r="E2" s="5" t="s">
-        <v>29</v>
+        <v>23</v>
       </c>
       <c r="F2" s="5" t="s">
-        <v>28</v>
-      </c>
-    </row>
-    <row r="3" spans="1:6" x14ac:dyDescent="0.35">
+        <v>22</v>
+      </c>
+    </row>
+    <row r="3" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A3" s="1">
         <v>1</v>
       </c>
@@ -661,258 +1101,772 @@
         <v>2</v>
       </c>
       <c r="C3" s="1" t="s">
-        <v>22</v>
-      </c>
-      <c r="D3" s="3"/>
+        <v>16</v>
+      </c>
+      <c r="D3" s="8" t="s">
+        <v>37</v>
+      </c>
       <c r="E3" s="1"/>
       <c r="F3" s="1"/>
     </row>
-    <row r="4" spans="1:6" x14ac:dyDescent="0.35">
-      <c r="A4" s="1">
-        <v>2</v>
-      </c>
-      <c r="B4" s="1" t="s">
-        <v>5</v>
-      </c>
-      <c r="C4" s="1" t="s">
-        <v>23</v>
-      </c>
-      <c r="D4" s="3"/>
+    <row r="4" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A4" s="1"/>
+      <c r="B4" s="1"/>
+      <c r="C4" s="1"/>
+      <c r="D4" s="8" t="s">
+        <v>38</v>
+      </c>
       <c r="E4" s="1"/>
       <c r="F4" s="1"/>
     </row>
-    <row r="5" spans="1:6" x14ac:dyDescent="0.35">
-      <c r="A5" s="1">
-        <v>3</v>
-      </c>
-      <c r="B5" s="1" t="s">
-        <v>30</v>
-      </c>
+    <row r="5" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A5" s="1"/>
+      <c r="B5" s="1"/>
       <c r="C5" s="1"/>
-      <c r="D5" s="3"/>
+      <c r="D5" s="8" t="s">
+        <v>39</v>
+      </c>
       <c r="E5" s="1"/>
       <c r="F5" s="1"/>
     </row>
-    <row r="6" spans="1:6" x14ac:dyDescent="0.35">
+    <row r="6" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A6" s="1">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="B6" s="1" t="s">
-        <v>31</v>
-      </c>
-      <c r="C6" s="1"/>
+        <v>5</v>
+      </c>
+      <c r="C6" s="1" t="s">
+        <v>17</v>
+      </c>
       <c r="D6" s="3"/>
       <c r="E6" s="1"/>
       <c r="F6" s="1"/>
     </row>
-    <row r="7" spans="1:6" x14ac:dyDescent="0.35">
-      <c r="A7" s="1">
-        <v>5</v>
-      </c>
-      <c r="B7" s="1" t="s">
-        <v>32</v>
-      </c>
+    <row r="7" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A7" s="1"/>
+      <c r="B7" s="1"/>
       <c r="C7" s="1"/>
-      <c r="D7" s="3"/>
+      <c r="D7" s="3" t="s">
+        <v>40</v>
+      </c>
       <c r="E7" s="1"/>
       <c r="F7" s="1"/>
     </row>
-    <row r="8" spans="1:6" x14ac:dyDescent="0.35">
-      <c r="A8" s="1">
-        <v>6</v>
-      </c>
-      <c r="B8" s="1" t="s">
-        <v>33</v>
-      </c>
+    <row r="8" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A8" s="1"/>
+      <c r="B8" s="1"/>
       <c r="C8" s="1"/>
-      <c r="D8" s="3"/>
+      <c r="D8" s="3" t="s">
+        <v>41</v>
+      </c>
       <c r="E8" s="1"/>
       <c r="F8" s="1"/>
     </row>
-    <row r="9" spans="1:6" x14ac:dyDescent="0.35">
-      <c r="A9" s="1">
-        <v>7</v>
-      </c>
-      <c r="B9" s="1" t="s">
+    <row r="9" spans="1:6" ht="50.4" x14ac:dyDescent="0.3">
+      <c r="A9" s="1"/>
+      <c r="B9" s="1"/>
+      <c r="C9" s="1"/>
+      <c r="D9" s="8" t="s">
+        <v>42</v>
+      </c>
+      <c r="E9" s="1"/>
+      <c r="F9" s="4" t="s">
+        <v>44</v>
+      </c>
+    </row>
+    <row r="10" spans="1:6" ht="50.4" x14ac:dyDescent="0.3">
+      <c r="A10" s="1"/>
+      <c r="B10" s="1"/>
+      <c r="C10" s="1"/>
+      <c r="D10" s="8" t="s">
+        <v>43</v>
+      </c>
+      <c r="E10" s="1"/>
+      <c r="F10" s="4" t="s">
+        <v>45</v>
+      </c>
+    </row>
+    <row r="11" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A11" s="1"/>
+      <c r="B11" s="1"/>
+      <c r="C11" s="1"/>
+      <c r="D11" s="8" t="s">
+        <v>46</v>
+      </c>
+      <c r="E11" s="1"/>
+      <c r="F11" s="4"/>
+    </row>
+    <row r="12" spans="1:6" ht="67.2" x14ac:dyDescent="0.3">
+      <c r="A12" s="1"/>
+      <c r="B12" s="1"/>
+      <c r="C12" s="1"/>
+      <c r="D12" s="8" t="s">
+        <v>47</v>
+      </c>
+      <c r="E12" s="1"/>
+      <c r="F12" s="10" t="s">
+        <v>48</v>
+      </c>
+    </row>
+    <row r="13" spans="1:6" ht="67.2" x14ac:dyDescent="0.3">
+      <c r="A13" s="1"/>
+      <c r="B13" s="1"/>
+      <c r="C13" s="1"/>
+      <c r="D13" s="8" t="s">
+        <v>49</v>
+      </c>
+      <c r="E13" s="1"/>
+      <c r="F13" s="4" t="s">
+        <v>51</v>
+      </c>
+    </row>
+    <row r="14" spans="1:6" ht="33.6" x14ac:dyDescent="0.3">
+      <c r="A14" s="1"/>
+      <c r="B14" s="1"/>
+      <c r="C14" s="1"/>
+      <c r="D14" s="8" t="s">
+        <v>50</v>
+      </c>
+      <c r="E14" s="1"/>
+      <c r="F14" s="4" t="s">
+        <v>52</v>
+      </c>
+    </row>
+    <row r="15" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A15" s="1"/>
+      <c r="B15" s="1"/>
+      <c r="C15" s="1"/>
+      <c r="D15" s="8" t="s">
+        <v>53</v>
+      </c>
+      <c r="E15" s="1"/>
+      <c r="F15" s="4"/>
+    </row>
+    <row r="16" spans="1:6" ht="50.4" x14ac:dyDescent="0.3">
+      <c r="A16" s="1"/>
+      <c r="B16" s="1"/>
+      <c r="C16" s="1"/>
+      <c r="D16" s="8" t="s">
+        <v>54</v>
+      </c>
+      <c r="E16" s="1"/>
+      <c r="F16" s="4" t="s">
+        <v>55</v>
+      </c>
+    </row>
+    <row r="17" spans="1:12" x14ac:dyDescent="0.3">
+      <c r="A17" s="1"/>
+      <c r="B17" s="1"/>
+      <c r="C17" s="1"/>
+      <c r="D17" s="8" t="s">
+        <v>56</v>
+      </c>
+      <c r="E17" s="1"/>
+      <c r="F17" s="4"/>
+    </row>
+    <row r="18" spans="1:12" x14ac:dyDescent="0.3">
+      <c r="A18" s="1"/>
+      <c r="B18" s="1"/>
+      <c r="C18" s="1"/>
+      <c r="D18" s="8" t="s">
+        <v>58</v>
+      </c>
+      <c r="E18" s="1"/>
+      <c r="F18" s="4" t="s">
+        <v>59</v>
+      </c>
+    </row>
+    <row r="19" spans="1:12" ht="409.6" x14ac:dyDescent="0.3">
+      <c r="A19" s="1">
+        <v>3</v>
+      </c>
+      <c r="B19" s="1" t="s">
         <v>24</v>
       </c>
-      <c r="C9" s="1" t="s">
+      <c r="C19" s="1"/>
+      <c r="D19" s="9" t="s">
+        <v>34</v>
+      </c>
+      <c r="E19" s="1"/>
+      <c r="F19" s="4" t="s">
+        <v>36</v>
+      </c>
+      <c r="G19" s="7" t="s">
+        <v>28</v>
+      </c>
+      <c r="H19" s="7" t="s">
+        <v>29</v>
+      </c>
+      <c r="I19" s="7" t="s">
+        <v>30</v>
+      </c>
+      <c r="J19" s="7" t="s">
+        <v>31</v>
+      </c>
+      <c r="K19" s="7" t="s">
+        <v>32</v>
+      </c>
+      <c r="L19" s="7" t="s">
+        <v>33</v>
+      </c>
+    </row>
+    <row r="20" spans="1:12" ht="100.8" x14ac:dyDescent="0.3">
+      <c r="A20" s="1"/>
+      <c r="B20" s="1"/>
+      <c r="C20" s="1"/>
+      <c r="D20" s="8"/>
+      <c r="E20" s="1"/>
+      <c r="F20" s="4" t="s">
+        <v>35</v>
+      </c>
+      <c r="G20" s="7"/>
+      <c r="H20" s="7"/>
+      <c r="I20" s="7"/>
+      <c r="J20" s="7"/>
+      <c r="K20" s="7"/>
+      <c r="L20" s="7"/>
+    </row>
+    <row r="21" spans="1:12" x14ac:dyDescent="0.3">
+      <c r="A21" s="1">
+        <v>4</v>
+      </c>
+      <c r="B21" s="1" t="s">
         <v>25</v>
       </c>
-      <c r="D9" s="3"/>
-      <c r="E9" s="1"/>
-      <c r="F9" s="1"/>
-    </row>
-    <row r="10" spans="1:6" x14ac:dyDescent="0.35">
-      <c r="A10" s="1">
-        <v>8</v>
-      </c>
-      <c r="B10" s="1" t="s">
-        <v>26</v>
-      </c>
-      <c r="C10" s="1"/>
-      <c r="D10" s="3"/>
-      <c r="E10" s="1"/>
-      <c r="F10" s="4"/>
-    </row>
-    <row r="11" spans="1:6" x14ac:dyDescent="0.35">
-      <c r="A11" s="1">
-        <v>9</v>
-      </c>
-      <c r="B11" s="1" t="s">
-        <v>6</v>
-      </c>
-      <c r="C11" s="1"/>
-      <c r="D11" s="3"/>
-      <c r="E11" s="1"/>
-      <c r="F11" s="1"/>
-    </row>
-    <row r="12" spans="1:6" x14ac:dyDescent="0.35">
-      <c r="A12" s="1">
-        <v>10</v>
-      </c>
-      <c r="B12" s="1" t="s">
-        <v>7</v>
-      </c>
-      <c r="C12" s="1"/>
-      <c r="D12" s="3"/>
-      <c r="E12" s="1"/>
-      <c r="F12" s="1"/>
-    </row>
-    <row r="13" spans="1:6" x14ac:dyDescent="0.35">
-      <c r="A13" s="1">
-        <v>11</v>
-      </c>
-      <c r="B13" s="1" t="s">
-        <v>27</v>
-      </c>
-      <c r="C13" s="1"/>
-      <c r="D13" s="3"/>
-      <c r="E13" s="1"/>
-      <c r="F13" s="1"/>
-    </row>
-    <row r="14" spans="1:6" x14ac:dyDescent="0.35">
-      <c r="A14" s="1">
-        <v>12</v>
-      </c>
-      <c r="B14" s="1" t="s">
-        <v>8</v>
-      </c>
-      <c r="C14" s="1"/>
-      <c r="D14" s="1"/>
-      <c r="E14" s="1"/>
-      <c r="F14" s="1"/>
-    </row>
-    <row r="15" spans="1:6" x14ac:dyDescent="0.35">
-      <c r="A15" s="1">
-        <v>13</v>
-      </c>
-      <c r="B15" s="1" t="s">
-        <v>9</v>
-      </c>
-      <c r="C15" s="1"/>
-      <c r="D15" s="1"/>
-      <c r="E15" s="1"/>
-      <c r="F15" s="1"/>
-    </row>
-    <row r="16" spans="1:6" x14ac:dyDescent="0.35">
-      <c r="A16" s="1">
-        <v>14</v>
-      </c>
-      <c r="B16" s="1" t="s">
-        <v>10</v>
-      </c>
-      <c r="C16" s="1"/>
-      <c r="D16" s="1"/>
-      <c r="E16" s="1"/>
-      <c r="F16" s="1"/>
-    </row>
-    <row r="17" spans="1:6" x14ac:dyDescent="0.35">
-      <c r="A17" s="1">
-        <v>15</v>
-      </c>
-      <c r="B17" s="1" t="s">
-        <v>11</v>
-      </c>
-      <c r="C17" s="1"/>
-      <c r="D17" s="1"/>
-      <c r="E17" s="1"/>
-      <c r="F17" s="1"/>
-    </row>
-    <row r="18" spans="1:6" x14ac:dyDescent="0.35">
-      <c r="A18" s="1">
-        <v>16</v>
-      </c>
-      <c r="B18" s="1" t="s">
-        <v>12</v>
-      </c>
-      <c r="C18" s="1"/>
-      <c r="D18" s="1"/>
-      <c r="E18" s="1"/>
-      <c r="F18" s="1"/>
-    </row>
-    <row r="19" spans="1:6" x14ac:dyDescent="0.35">
-      <c r="A19" s="1">
-        <v>17</v>
-      </c>
-      <c r="B19" s="1" t="s">
-        <v>13</v>
-      </c>
-      <c r="C19" s="1"/>
-      <c r="D19" s="1"/>
-      <c r="E19" s="1"/>
-      <c r="F19" s="1"/>
-    </row>
-    <row r="20" spans="1:6" x14ac:dyDescent="0.35">
-      <c r="A20" s="1">
-        <v>18</v>
-      </c>
-      <c r="B20" s="1" t="s">
-        <v>14</v>
-      </c>
-      <c r="C20" s="1"/>
-      <c r="D20" s="1"/>
-      <c r="E20" s="1"/>
-      <c r="F20" s="1"/>
-    </row>
-    <row r="21" spans="1:6" x14ac:dyDescent="0.35">
-      <c r="A21" s="1">
-        <v>19</v>
-      </c>
-      <c r="B21" s="1" t="s">
-        <v>15</v>
-      </c>
       <c r="C21" s="1"/>
-      <c r="D21" s="1"/>
+      <c r="D21" s="8" t="s">
+        <v>60</v>
+      </c>
       <c r="E21" s="1"/>
       <c r="F21" s="1"/>
     </row>
-    <row r="22" spans="1:6" x14ac:dyDescent="0.35">
-      <c r="A22" s="1">
-        <v>20</v>
-      </c>
-      <c r="B22" s="1" t="s">
-        <v>16</v>
-      </c>
+    <row r="22" spans="1:12" x14ac:dyDescent="0.3">
+      <c r="A22" s="1"/>
+      <c r="B22" s="1"/>
       <c r="C22" s="1"/>
-      <c r="D22" s="1"/>
+      <c r="D22" s="8" t="s">
+        <v>61</v>
+      </c>
       <c r="E22" s="1"/>
       <c r="F22" s="1"/>
     </row>
-    <row r="23" spans="1:6" x14ac:dyDescent="0.35">
-      <c r="A23" s="1">
-        <v>21</v>
-      </c>
-      <c r="B23" s="1" t="s">
-        <v>17</v>
-      </c>
+    <row r="23" spans="1:12" x14ac:dyDescent="0.3">
+      <c r="A23" s="1"/>
+      <c r="B23" s="1"/>
       <c r="C23" s="1"/>
-      <c r="D23" s="1"/>
+      <c r="D23" s="8" t="s">
+        <v>62</v>
+      </c>
       <c r="E23" s="1"/>
       <c r="F23" s="1"/>
     </row>
+    <row r="24" spans="1:12" x14ac:dyDescent="0.3">
+      <c r="A24" s="1">
+        <v>5</v>
+      </c>
+      <c r="B24" s="1" t="s">
+        <v>26</v>
+      </c>
+      <c r="C24" s="1"/>
+      <c r="D24" s="8"/>
+      <c r="E24" s="1"/>
+      <c r="F24" s="1"/>
+    </row>
+    <row r="25" spans="1:12" x14ac:dyDescent="0.3">
+      <c r="A25" s="1"/>
+      <c r="B25" s="1"/>
+      <c r="C25" s="1"/>
+      <c r="D25" s="11" t="s">
+        <v>57</v>
+      </c>
+      <c r="E25" s="1"/>
+      <c r="F25" s="1"/>
+    </row>
+    <row r="26" spans="1:12" x14ac:dyDescent="0.3">
+      <c r="A26" s="1"/>
+      <c r="B26" s="1"/>
+      <c r="C26" s="1"/>
+      <c r="D26" s="8" t="s">
+        <v>63</v>
+      </c>
+      <c r="E26" s="1"/>
+      <c r="F26" s="1"/>
+    </row>
+    <row r="27" spans="1:12" x14ac:dyDescent="0.3">
+      <c r="A27" s="1"/>
+      <c r="B27" s="1"/>
+      <c r="C27" s="1"/>
+      <c r="D27" s="11" t="s">
+        <v>64</v>
+      </c>
+      <c r="E27" s="1"/>
+      <c r="F27" s="1"/>
+    </row>
+    <row r="28" spans="1:12" x14ac:dyDescent="0.3">
+      <c r="A28" s="1">
+        <v>6</v>
+      </c>
+      <c r="B28" s="1" t="s">
+        <v>27</v>
+      </c>
+      <c r="C28" s="1"/>
+      <c r="D28" s="3"/>
+      <c r="E28" s="1"/>
+      <c r="F28" s="1"/>
+    </row>
+    <row r="29" spans="1:12" x14ac:dyDescent="0.3">
+      <c r="A29" s="1"/>
+      <c r="B29" s="1"/>
+      <c r="C29" s="1"/>
+      <c r="D29" s="8" t="s">
+        <v>65</v>
+      </c>
+      <c r="E29" s="1"/>
+      <c r="F29" s="1"/>
+    </row>
+    <row r="30" spans="1:12" x14ac:dyDescent="0.3">
+      <c r="A30" s="1"/>
+      <c r="B30" s="1"/>
+      <c r="C30" s="1"/>
+      <c r="D30" s="8" t="s">
+        <v>66</v>
+      </c>
+      <c r="E30" s="1"/>
+      <c r="F30" s="1"/>
+    </row>
+    <row r="31" spans="1:12" x14ac:dyDescent="0.3">
+      <c r="A31" s="1"/>
+      <c r="B31" s="1"/>
+      <c r="C31" s="1"/>
+      <c r="D31" s="8" t="s">
+        <v>67</v>
+      </c>
+      <c r="E31" s="1"/>
+      <c r="F31" s="1"/>
+    </row>
+    <row r="32" spans="1:12" x14ac:dyDescent="0.3">
+      <c r="A32" s="1">
+        <v>7</v>
+      </c>
+      <c r="B32" s="1" t="s">
+        <v>18</v>
+      </c>
+      <c r="C32" s="1" t="s">
+        <v>19</v>
+      </c>
+      <c r="D32" s="3"/>
+      <c r="E32" s="1"/>
+      <c r="F32" s="1"/>
+    </row>
+    <row r="33" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A33" s="1"/>
+      <c r="B33" s="1"/>
+      <c r="C33" s="1"/>
+      <c r="D33" s="3"/>
+      <c r="E33" s="1"/>
+      <c r="F33" s="1"/>
+    </row>
+    <row r="34" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A34" s="1"/>
+      <c r="B34" s="1"/>
+      <c r="C34" s="1"/>
+      <c r="D34" s="3"/>
+      <c r="E34" s="1"/>
+      <c r="F34" s="1"/>
+    </row>
+    <row r="35" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A35" s="1"/>
+      <c r="B35" s="1"/>
+      <c r="C35" s="1"/>
+      <c r="D35" s="3"/>
+      <c r="E35" s="1"/>
+      <c r="F35" s="1"/>
+    </row>
+    <row r="36" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A36" s="1">
+        <v>8</v>
+      </c>
+      <c r="B36" s="1" t="s">
+        <v>20</v>
+      </c>
+      <c r="C36" s="1"/>
+      <c r="D36" s="3"/>
+      <c r="E36" s="1"/>
+      <c r="F36" s="4"/>
+    </row>
+    <row r="37" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A37" s="1"/>
+      <c r="B37" s="1"/>
+      <c r="C37" s="1"/>
+      <c r="D37" s="8" t="s">
+        <v>68</v>
+      </c>
+      <c r="E37" s="1"/>
+      <c r="F37" s="4"/>
+    </row>
+    <row r="38" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A38" s="1"/>
+      <c r="B38" s="1"/>
+      <c r="C38" s="1"/>
+      <c r="D38" s="8" t="s">
+        <v>68</v>
+      </c>
+      <c r="E38" s="1"/>
+      <c r="F38" s="4"/>
+    </row>
+    <row r="39" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A39" s="1"/>
+      <c r="B39" s="1"/>
+      <c r="C39" s="1"/>
+      <c r="D39" s="8" t="s">
+        <v>69</v>
+      </c>
+      <c r="E39" s="1"/>
+      <c r="F39" s="4"/>
+    </row>
+    <row r="40" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A40" s="1">
+        <v>9</v>
+      </c>
+      <c r="B40" s="1" t="s">
+        <v>6</v>
+      </c>
+      <c r="C40" s="1"/>
+      <c r="D40" s="3"/>
+      <c r="E40" s="1"/>
+      <c r="F40" s="1"/>
+    </row>
+    <row r="41" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A41" s="1"/>
+      <c r="B41" s="1"/>
+      <c r="C41" s="1"/>
+      <c r="D41" s="8" t="s">
+        <v>70</v>
+      </c>
+      <c r="E41" s="1"/>
+      <c r="F41" s="1"/>
+    </row>
+    <row r="42" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A42" s="1"/>
+      <c r="B42" s="1"/>
+      <c r="C42" s="1"/>
+      <c r="D42" s="11" t="s">
+        <v>71</v>
+      </c>
+      <c r="E42" s="1"/>
+      <c r="F42" s="1"/>
+    </row>
+    <row r="43" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A43" s="1"/>
+      <c r="B43" s="1"/>
+      <c r="C43" s="1"/>
+      <c r="D43" s="8" t="s">
+        <v>72</v>
+      </c>
+      <c r="E43" s="1"/>
+      <c r="F43" s="1"/>
+    </row>
+    <row r="44" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A44" s="1">
+        <v>10</v>
+      </c>
+      <c r="B44" s="1" t="s">
+        <v>7</v>
+      </c>
+      <c r="C44" s="1"/>
+      <c r="D44" s="3"/>
+      <c r="E44" s="1"/>
+      <c r="F44" s="1"/>
+    </row>
+    <row r="45" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A45" s="1"/>
+      <c r="B45" s="1"/>
+      <c r="C45" s="1"/>
+      <c r="D45" s="8" t="s">
+        <v>73</v>
+      </c>
+      <c r="E45" s="1"/>
+      <c r="F45" s="1"/>
+    </row>
+    <row r="46" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A46" s="1"/>
+      <c r="B46" s="1"/>
+      <c r="C46" s="1"/>
+      <c r="D46" s="8" t="s">
+        <v>74</v>
+      </c>
+      <c r="E46" s="1"/>
+      <c r="F46" s="1"/>
+    </row>
+    <row r="47" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A47" s="1"/>
+      <c r="B47" s="1"/>
+      <c r="C47" s="1"/>
+      <c r="D47" s="8" t="s">
+        <v>75</v>
+      </c>
+      <c r="E47" s="1"/>
+      <c r="F47" s="1"/>
+    </row>
+    <row r="48" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A48" s="1">
+        <v>11</v>
+      </c>
+      <c r="B48" s="1" t="s">
+        <v>21</v>
+      </c>
+      <c r="C48" s="1"/>
+      <c r="D48" s="3"/>
+      <c r="E48" s="1"/>
+      <c r="F48" s="1"/>
+    </row>
+    <row r="49" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A49" s="1"/>
+      <c r="B49" s="1"/>
+      <c r="C49" s="1"/>
+      <c r="D49" s="8" t="s">
+        <v>76</v>
+      </c>
+      <c r="E49" s="1"/>
+      <c r="F49" s="1"/>
+    </row>
+    <row r="50" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A50" s="1"/>
+      <c r="B50" s="1"/>
+      <c r="C50" s="1"/>
+      <c r="D50" s="8" t="s">
+        <v>77</v>
+      </c>
+      <c r="E50" s="1"/>
+      <c r="F50" s="1"/>
+    </row>
+    <row r="51" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A51" s="1"/>
+      <c r="B51" s="1"/>
+      <c r="C51" s="1"/>
+      <c r="D51" s="8" t="s">
+        <v>78</v>
+      </c>
+      <c r="E51" s="1"/>
+      <c r="F51" s="1"/>
+    </row>
+    <row r="52" spans="1:6" ht="16.2" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A52" s="1">
+        <v>12</v>
+      </c>
+      <c r="B52" s="1" t="s">
+        <v>8</v>
+      </c>
+      <c r="C52" s="1"/>
+      <c r="D52" s="1"/>
+      <c r="E52" s="1"/>
+      <c r="F52" s="1"/>
+    </row>
+    <row r="53" spans="1:6" ht="16.2" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A53" s="1"/>
+      <c r="B53" s="1"/>
+      <c r="C53" s="1"/>
+      <c r="D53" s="8" t="s">
+        <v>79</v>
+      </c>
+      <c r="E53" s="1"/>
+      <c r="F53" s="1"/>
+    </row>
+    <row r="54" spans="1:6" ht="43.2" x14ac:dyDescent="0.3">
+      <c r="A54" s="1"/>
+      <c r="B54" s="1"/>
+      <c r="C54" s="1"/>
+      <c r="D54" s="9" t="s">
+        <v>80</v>
+      </c>
+      <c r="E54" s="1"/>
+      <c r="F54" s="1"/>
+    </row>
+    <row r="55" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A55" s="1"/>
+      <c r="B55" s="1"/>
+      <c r="C55" s="1"/>
+      <c r="D55" s="8" t="s">
+        <v>81</v>
+      </c>
+      <c r="E55" s="1"/>
+      <c r="F55" s="1"/>
+    </row>
+    <row r="56" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A56" s="1">
+        <v>13</v>
+      </c>
+      <c r="B56" s="1" t="s">
+        <v>9</v>
+      </c>
+      <c r="C56" s="1"/>
+      <c r="D56" s="1"/>
+      <c r="E56" s="1"/>
+      <c r="F56" s="1"/>
+    </row>
+    <row r="57" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A57" s="1"/>
+      <c r="B57" s="1"/>
+      <c r="C57" s="1"/>
+      <c r="D57" s="8" t="s">
+        <v>82</v>
+      </c>
+      <c r="E57" s="1"/>
+      <c r="F57" s="1"/>
+    </row>
+    <row r="58" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A58" s="1"/>
+      <c r="B58" s="1"/>
+      <c r="C58" s="1"/>
+      <c r="D58" s="8" t="s">
+        <v>83</v>
+      </c>
+      <c r="E58" s="1"/>
+      <c r="F58" s="1"/>
+    </row>
+    <row r="59" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A59" s="1"/>
+      <c r="B59" s="1"/>
+      <c r="C59" s="1"/>
+      <c r="D59" s="8" t="s">
+        <v>84</v>
+      </c>
+      <c r="E59" s="1"/>
+      <c r="F59" s="1"/>
+    </row>
+    <row r="60" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A60" s="1">
+        <v>14</v>
+      </c>
+      <c r="B60" s="1" t="s">
+        <v>10</v>
+      </c>
+      <c r="C60" s="1"/>
+      <c r="D60" s="1"/>
+      <c r="E60" s="1"/>
+      <c r="F60" s="1"/>
+    </row>
+    <row r="61" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A61" s="1"/>
+      <c r="B61" s="1"/>
+      <c r="C61" s="1"/>
+      <c r="D61" s="8" t="s">
+        <v>85</v>
+      </c>
+      <c r="E61" s="1"/>
+      <c r="F61" s="1"/>
+    </row>
+    <row r="62" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A62" s="1"/>
+      <c r="B62" s="1"/>
+      <c r="C62" s="1"/>
+      <c r="D62" s="8" t="s">
+        <v>86</v>
+      </c>
+      <c r="E62" s="1"/>
+      <c r="F62" s="1"/>
+    </row>
+    <row r="63" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A63" s="1"/>
+      <c r="B63" s="1"/>
+      <c r="C63" s="1"/>
+      <c r="D63" s="8" t="s">
+        <v>87</v>
+      </c>
+      <c r="E63" s="1"/>
+      <c r="F63" s="1"/>
+    </row>
+    <row r="64" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A64" s="1">
+        <v>18</v>
+      </c>
+      <c r="B64" s="1" t="s">
+        <v>11</v>
+      </c>
+      <c r="C64" s="1"/>
+      <c r="E64" s="1"/>
+      <c r="F64" s="1"/>
+    </row>
+    <row r="65" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A65" s="1"/>
+      <c r="B65" s="1"/>
+      <c r="C65" s="1"/>
+      <c r="D65" s="8" t="s">
+        <v>88</v>
+      </c>
+      <c r="E65" s="1"/>
+      <c r="F65" s="1"/>
+    </row>
+    <row r="66" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A66" s="1"/>
+      <c r="B66" s="1"/>
+      <c r="C66" s="1"/>
+      <c r="D66" s="8" t="s">
+        <v>89</v>
+      </c>
+      <c r="E66" s="1"/>
+      <c r="F66" s="1"/>
+    </row>
+    <row r="67" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A67" s="1"/>
+      <c r="B67" s="1"/>
+      <c r="C67" s="1"/>
+      <c r="D67" s="8" t="s">
+        <v>90</v>
+      </c>
+      <c r="E67" s="1"/>
+      <c r="F67" s="1"/>
+    </row>
   </sheetData>
+  <hyperlinks>
+    <hyperlink ref="D19" r:id="rId1" xr:uid="{1A58C001-5CA8-4698-80C0-8E9AE993DCFE}"/>
+    <hyperlink ref="D3" r:id="rId2" xr:uid="{CBEFF935-43B0-4678-9E84-68B644F90B2F}"/>
+    <hyperlink ref="D4" r:id="rId3" xr:uid="{633A55FD-AC9E-4CC7-9C45-F483B7B86CC6}"/>
+    <hyperlink ref="D5" r:id="rId4" xr:uid="{C376D87F-A4F7-4EBA-9E54-34E9C25C3A82}"/>
+    <hyperlink ref="D9" r:id="rId5" xr:uid="{3D4CDB3D-FD7D-4C96-A284-D41AD758067D}"/>
+    <hyperlink ref="D10" r:id="rId6" xr:uid="{6E67B1FB-A93C-4545-8E38-61C200CB2B2B}"/>
+    <hyperlink ref="D12" r:id="rId7" xr:uid="{F3F87AC7-D2DF-4FC2-A558-288F3C41852C}"/>
+    <hyperlink ref="D13" r:id="rId8" xr:uid="{DC1A27B0-76E1-46DA-8229-EE5213A97D5A}"/>
+    <hyperlink ref="D14" r:id="rId9" xr:uid="{538E1B02-D115-4BE0-B10B-C4155EEB2BA3}"/>
+    <hyperlink ref="D16" r:id="rId10" xr:uid="{F41F0039-D81A-4C99-8C16-55823C8410C4}"/>
+    <hyperlink ref="D17" r:id="rId11" xr:uid="{83CCC76D-FE94-4FC4-BF27-CFE9109A671F}"/>
+    <hyperlink ref="D18" r:id="rId12" xr:uid="{7E79A88D-4206-4763-A8D4-74CAFB94C7D7}"/>
+    <hyperlink ref="D21" r:id="rId13" xr:uid="{ED86CCA8-0EAD-491F-AA9E-FA3C5C488EA3}"/>
+    <hyperlink ref="D22" r:id="rId14" xr:uid="{17B39EB6-358C-480D-909B-37DAB741C407}"/>
+    <hyperlink ref="D23" r:id="rId15" xr:uid="{5951153B-15DB-4D2D-B42F-B7342FB517A9}"/>
+    <hyperlink ref="D25" r:id="rId16" xr:uid="{E5858E9F-8347-40E4-AB68-FDC60759EEE0}"/>
+    <hyperlink ref="D26" r:id="rId17" xr:uid="{9A46811D-9BC9-45FB-BE9A-6C9AAE3B0B8A}"/>
+    <hyperlink ref="D27" r:id="rId18" xr:uid="{8886B4E4-E47E-4AFA-84B2-98EC5C0446AE}"/>
+    <hyperlink ref="D29" r:id="rId19" xr:uid="{20AF3F9E-8477-4D5A-8A6F-5543FDF4707C}"/>
+    <hyperlink ref="D30" r:id="rId20" xr:uid="{B0AD597E-0EA7-41D4-A4D7-E9EF74B7A734}"/>
+    <hyperlink ref="D31" r:id="rId21" xr:uid="{F5F2B4AD-B15D-4C92-A1EA-A57127911B9D}"/>
+    <hyperlink ref="D37" r:id="rId22" xr:uid="{4624F232-3D34-48DC-B415-7CECCADC42B8}"/>
+    <hyperlink ref="D38" r:id="rId23" xr:uid="{A4A6056C-13F1-465A-B54A-2281951CD475}"/>
+    <hyperlink ref="D39" r:id="rId24" xr:uid="{BFA899E4-939B-43CC-82B6-1D70058F8977}"/>
+    <hyperlink ref="D41" r:id="rId25" xr:uid="{2A075F6E-1EE1-474C-8E56-C65551051CA4}"/>
+    <hyperlink ref="D42" r:id="rId26" xr:uid="{B5D1459A-5F0F-4959-A99E-C4E39D53D64B}"/>
+    <hyperlink ref="D43" r:id="rId27" xr:uid="{DCE145DC-0FDF-4700-8929-6CF19C89DD5D}"/>
+    <hyperlink ref="D45" r:id="rId28" xr:uid="{60E5CF1B-4F4B-4488-9935-6D81F8E339EB}"/>
+    <hyperlink ref="D46" r:id="rId29" xr:uid="{A0FE471F-1C7C-4FB9-B7EF-50EC473AABD6}"/>
+    <hyperlink ref="D47" r:id="rId30" xr:uid="{154285D1-D400-4BD4-9DDB-4727FB3E5293}"/>
+    <hyperlink ref="D49" r:id="rId31" xr:uid="{812D3FEE-6E5E-4F47-A8F5-AE68E5657B67}"/>
+    <hyperlink ref="D50" r:id="rId32" xr:uid="{C6A20CB6-75D4-4709-A8B7-BE33D4151F28}"/>
+    <hyperlink ref="D51" r:id="rId33" xr:uid="{9481162F-6F82-4DFA-B0C2-E18BB687952D}"/>
+    <hyperlink ref="D53" r:id="rId34" xr:uid="{CFD02D36-72A8-42B1-A4DE-1C9C2D861C73}"/>
+    <hyperlink ref="D54" r:id="rId35" display="https://github.com/nandland/spi-master.git" xr:uid="{53416F16-2477-4686-8E87-A8AD8D7CCC1F}"/>
+    <hyperlink ref="D55" r:id="rId36" xr:uid="{A99AFE91-E40C-499F-A378-DB0E4A9752C6}"/>
+    <hyperlink ref="D57" r:id="rId37" xr:uid="{4A875C94-4153-46A6-A61F-36FE74223FE7}"/>
+    <hyperlink ref="D58" r:id="rId38" xr:uid="{2ED8102E-B72A-4D1E-A759-58E935F46969}"/>
+    <hyperlink ref="D59" r:id="rId39" xr:uid="{DFBBC5CD-3D9D-418E-8066-231683E4BDF4}"/>
+    <hyperlink ref="D61" r:id="rId40" xr:uid="{7DC12D53-CADF-41F0-84FA-EC3FEF8D2B09}"/>
+    <hyperlink ref="D62" r:id="rId41" xr:uid="{E6D5499C-381E-4F21-AC15-85498A547D9F}"/>
+    <hyperlink ref="D63" r:id="rId42" xr:uid="{23D43F97-F3BD-4B09-B054-21598B4266EC}"/>
+    <hyperlink ref="D65" r:id="rId43" xr:uid="{17E1119E-5558-4FBE-8345-09B1C036E379}"/>
+    <hyperlink ref="D66" r:id="rId44" xr:uid="{6C304B39-61E6-4B75-9A64-ECE8CBB3A738}"/>
+    <hyperlink ref="D67" r:id="rId45" xr:uid="{BE0F3DB2-2E1A-4DB0-94E3-DFA902B71F20}"/>
+  </hyperlinks>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
-  <pageSetup orientation="portrait" r:id="rId1"/>
+  <pageSetup orientation="portrait" r:id="rId46"/>
 </worksheet>
 </file>
--- a/doc/001_OpenVLSI_Resource.xlsx
+++ b/doc/001_OpenVLSI_Resource.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\Git\VLSIT_SOC_Starter\doc\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{2586FFDB-FD4E-4E27-A962-1669B11CDB15}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{534174FB-E931-4D4D-B9EF-3A4EE710CE57}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="13896" activeTab="1" xr2:uid="{B6857A90-25D4-4A67-8903-7C0067D27823}"/>
   </bookViews>
@@ -36,7 +36,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="93" uniqueCount="91">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="96" uniqueCount="94">
   <si>
     <t>No.</t>
   </si>
@@ -546,12 +546,237 @@
   <si>
     <t>https://github.com/nguyenhong-hoa/WatchdogTimer.git</t>
   </si>
+  <si>
+    <r>
+      <t xml:space="preserve">Support </t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="13"/>
+        <color theme="1"/>
+        <rFont val="Arial"/>
+        <family val="2"/>
+      </rPr>
+      <t>outstading</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="13"/>
+        <color theme="1"/>
+        <rFont val="Arial"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve"> but </t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="13"/>
+        <color theme="1"/>
+        <rFont val="Arial"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">not out-of-order --&gt; Maybe
+</t>
+    </r>
+    <r>
+      <rPr>
+        <i/>
+        <sz val="13"/>
+        <color theme="1"/>
+        <rFont val="Arial"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">Responses always follow the </t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <i/>
+        <sz val="13"/>
+        <color theme="1"/>
+        <rFont val="Arial"/>
+        <family val="2"/>
+      </rPr>
+      <t>order of issue</t>
+    </r>
+    <r>
+      <rPr>
+        <i/>
+        <sz val="13"/>
+        <color theme="1"/>
+        <rFont val="Arial"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">
+or only support a </t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <i/>
+        <sz val="13"/>
+        <color theme="1"/>
+        <rFont val="Arial"/>
+        <family val="2"/>
+      </rPr>
+      <t>single AXI ID</t>
+    </r>
+    <r>
+      <rPr>
+        <i/>
+        <sz val="13"/>
+        <color theme="1"/>
+        <rFont val="Arial"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">
+or </t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <i/>
+        <sz val="13"/>
+        <color theme="1"/>
+        <rFont val="Arial"/>
+        <family val="2"/>
+      </rPr>
+      <t>serialize</t>
+    </r>
+    <r>
+      <rPr>
+        <i/>
+        <sz val="13"/>
+        <color theme="1"/>
+        <rFont val="Arial"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve"> down to AHB
+Because there is a separate FIFO for ID --&gt; it uses method "serialize down to AHB"/ </t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <i/>
+        <sz val="13"/>
+        <color theme="1"/>
+        <rFont val="Arial"/>
+        <family val="2"/>
+      </rPr>
+      <t>Support</t>
+    </r>
+    <r>
+      <rPr>
+        <i/>
+        <sz val="13"/>
+        <color theme="1"/>
+        <rFont val="Arial"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve"> multiple AXI ID/ Responses always follow the order of issue
+AXI </t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <i/>
+        <sz val="13"/>
+        <color theme="1"/>
+        <rFont val="Arial"/>
+        <family val="2"/>
+      </rPr>
+      <t>does not</t>
+    </r>
+    <r>
+      <rPr>
+        <i/>
+        <sz val="13"/>
+        <color theme="1"/>
+        <rFont val="Arial"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve"> support </t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <i/>
+        <sz val="13"/>
+        <color theme="1"/>
+        <rFont val="Arial"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">lock/exclusive </t>
+    </r>
+    <r>
+      <rPr>
+        <i/>
+        <sz val="13"/>
+        <color theme="1"/>
+        <rFont val="Arial"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">accces (do not exsit AWLOCK/ARLOCK and HLOCK is tied 0)
+*Need exclusive access cases: 
+     Multi-core CPU
+     Share-memory DMA coordination
+     Modern OS kernels
+Features:
+AXI3 (exists WID) - AHB-Lite (No retry no Slip / HRESP chỉ có OKAY/ERROR)
+</t>
+    </r>
+    <r>
+      <rPr>
+        <i/>
+        <u/>
+        <sz val="13"/>
+        <color theme="1"/>
+        <rFont val="Arial"/>
+        <family val="2"/>
+      </rPr>
+      <t>Note</t>
+    </r>
+    <r>
+      <rPr>
+        <i/>
+        <sz val="13"/>
+        <color theme="1"/>
+        <rFont val="Arial"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve"> WID exists; no write interleaving logic detected. Likely for mapping only.
+</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="13"/>
+        <color theme="1"/>
+        <rFont val="Arial"/>
+        <family val="2"/>
+      </rPr>
+      <t>Bit width: 32-bit address/ 64-bit data.
+2 clock domain (hclk, aclk/ exsist 2-flop synchronizer/ FIFOs use gray code)</t>
+    </r>
+  </si>
+  <si>
+    <t>- Interface
+- features
+'- function
+Tool generate</t>
+  </si>
+  <si>
+    <t xml:space="preserve">per README
+"The bridge does not implementAXI ID" and "Support FIXED/ INCR/ WRAP" -- &gt; Most likely AXI4
+</t>
+  </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
-  <fonts count="7" x14ac:knownFonts="1">
+  <fonts count="9" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -601,6 +826,22 @@
       <name val="Arial"/>
       <family val="2"/>
     </font>
+    <font>
+      <b/>
+      <i/>
+      <sz val="13"/>
+      <color theme="1"/>
+      <name val="Arial"/>
+      <family val="2"/>
+    </font>
+    <font>
+      <i/>
+      <u/>
+      <sz val="13"/>
+      <color theme="1"/>
+      <name val="Arial"/>
+      <family val="2"/>
+    </font>
   </fonts>
   <fills count="2">
     <fill>
@@ -638,7 +879,7 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
   </cellStyleXfs>
-  <cellXfs count="12">
+  <cellXfs count="13">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="center"/>
@@ -672,6 +913,9 @@
     </xf>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="1" applyAlignment="1">
       <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="1" xfId="0" quotePrefix="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center" wrapText="1"/>
     </xf>
   </cellXfs>
   <cellStyles count="2">
@@ -1327,7 +1571,7 @@
       <c r="K20" s="7"/>
       <c r="L20" s="7"/>
     </row>
-    <row r="21" spans="1:12" x14ac:dyDescent="0.3">
+    <row r="21" spans="1:12" ht="346.2" x14ac:dyDescent="0.3">
       <c r="A21" s="1">
         <v>4</v>
       </c>
@@ -1339,9 +1583,11 @@
         <v>60</v>
       </c>
       <c r="E21" s="1"/>
-      <c r="F21" s="1"/>
-    </row>
-    <row r="22" spans="1:12" x14ac:dyDescent="0.3">
+      <c r="F21" s="4" t="s">
+        <v>91</v>
+      </c>
+    </row>
+    <row r="22" spans="1:12" ht="67.2" x14ac:dyDescent="0.3">
       <c r="A22" s="1"/>
       <c r="B22" s="1"/>
       <c r="C22" s="1"/>
@@ -1349,9 +1595,11 @@
         <v>61</v>
       </c>
       <c r="E22" s="1"/>
-      <c r="F22" s="1"/>
-    </row>
-    <row r="23" spans="1:12" x14ac:dyDescent="0.3">
+      <c r="F22" s="12" t="s">
+        <v>92</v>
+      </c>
+    </row>
+    <row r="23" spans="1:12" ht="67.2" x14ac:dyDescent="0.3">
       <c r="A23" s="1"/>
       <c r="B23" s="1"/>
       <c r="C23" s="1"/>
@@ -1359,7 +1607,9 @@
         <v>62</v>
       </c>
       <c r="E23" s="1"/>
-      <c r="F23" s="1"/>
+      <c r="F23" s="4" t="s">
+        <v>93</v>
+      </c>
     </row>
     <row r="24" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A24" s="1">

--- a/doc/001_OpenVLSI_Resource.xlsx
+++ b/doc/001_OpenVLSI_Resource.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\Git\VLSIT_SOC_Starter\doc\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{534174FB-E931-4D4D-B9EF-3A4EE710CE57}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{F243152B-6ECF-4FF6-B003-3A0D6A01743E}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="13896" activeTab="1" xr2:uid="{B6857A90-25D4-4A67-8903-7C0067D27823}"/>
   </bookViews>
@@ -36,7 +36,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="96" uniqueCount="94">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="107" uniqueCount="95">
   <si>
     <t>No.</t>
   </si>
@@ -769,7 +769,14 @@
   <si>
     <t xml:space="preserve">per README
 "The bridge does not implementAXI ID" and "Support FIXED/ INCR/ WRAP" -- &gt; Most likely AXI4
+AHB-lite 
+The bitwidth parameter defaults to 32 both Address and Data
+Features:
+Exist FIFO
 </t>
+  </si>
+  <si>
+    <t>x</t>
   </si>
 </sst>
 </file>
@@ -1300,80 +1307,85 @@
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{53B9D3ED-3076-4299-B077-6E810E94CF83}">
-  <dimension ref="A2:L67"/>
+  <dimension ref="A2:M67"/>
   <sheetFormatPr defaultColWidth="8.77734375" defaultRowHeight="16.8" x14ac:dyDescent="0.3"/>
   <cols>
     <col min="1" max="1" width="4.33203125" style="2" bestFit="1" customWidth="1"/>
     <col min="2" max="2" width="18.88671875" style="2" bestFit="1" customWidth="1"/>
-    <col min="3" max="3" width="37.21875" style="2" customWidth="1"/>
-    <col min="4" max="4" width="78.21875" style="2" customWidth="1"/>
-    <col min="5" max="5" width="16.5546875" style="2" bestFit="1" customWidth="1"/>
-    <col min="6" max="6" width="83.21875" style="2" customWidth="1"/>
-    <col min="7" max="7" width="54.21875" style="2" customWidth="1"/>
-    <col min="8" max="8" width="39" style="2" customWidth="1"/>
-    <col min="9" max="9" width="54.77734375" style="2" customWidth="1"/>
-    <col min="10" max="10" width="49.109375" style="2" customWidth="1"/>
-    <col min="11" max="11" width="17.5546875" style="2" customWidth="1"/>
-    <col min="12" max="16384" width="8.77734375" style="2"/>
+    <col min="3" max="3" width="18.88671875" style="2" customWidth="1"/>
+    <col min="4" max="4" width="37.21875" style="2" customWidth="1"/>
+    <col min="5" max="5" width="78.21875" style="2" customWidth="1"/>
+    <col min="6" max="6" width="16.5546875" style="2" bestFit="1" customWidth="1"/>
+    <col min="7" max="7" width="83.21875" style="2" customWidth="1"/>
+    <col min="8" max="8" width="54.21875" style="2" customWidth="1"/>
+    <col min="9" max="9" width="39" style="2" customWidth="1"/>
+    <col min="10" max="10" width="54.77734375" style="2" customWidth="1"/>
+    <col min="11" max="11" width="49.109375" style="2" customWidth="1"/>
+    <col min="12" max="12" width="17.5546875" style="2" customWidth="1"/>
+    <col min="13" max="16384" width="8.77734375" style="2"/>
   </cols>
   <sheetData>
-    <row r="2" spans="1:6" s="6" customFormat="1" x14ac:dyDescent="0.3">
+    <row r="2" spans="1:7" s="6" customFormat="1" x14ac:dyDescent="0.3">
       <c r="A2" s="5" t="s">
         <v>0</v>
       </c>
       <c r="B2" s="5" t="s">
         <v>1</v>
       </c>
-      <c r="C2" s="5" t="s">
+      <c r="C2" s="5"/>
+      <c r="D2" s="5" t="s">
         <v>15</v>
       </c>
-      <c r="D2" s="5" t="s">
+      <c r="E2" s="5" t="s">
         <v>3</v>
       </c>
-      <c r="E2" s="5" t="s">
+      <c r="F2" s="5" t="s">
         <v>23</v>
       </c>
-      <c r="F2" s="5" t="s">
+      <c r="G2" s="5" t="s">
         <v>22</v>
       </c>
     </row>
-    <row r="3" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="3" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A3" s="1">
         <v>1</v>
       </c>
       <c r="B3" s="1" t="s">
         <v>2</v>
       </c>
-      <c r="C3" s="1" t="s">
+      <c r="C3" s="1"/>
+      <c r="D3" s="1" t="s">
         <v>16</v>
       </c>
-      <c r="D3" s="8" t="s">
+      <c r="E3" s="8" t="s">
         <v>37</v>
       </c>
-      <c r="E3" s="1"/>
       <c r="F3" s="1"/>
-    </row>
-    <row r="4" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="G3" s="1"/>
+    </row>
+    <row r="4" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A4" s="1"/>
       <c r="B4" s="1"/>
       <c r="C4" s="1"/>
-      <c r="D4" s="8" t="s">
+      <c r="D4" s="1"/>
+      <c r="E4" s="8" t="s">
         <v>38</v>
       </c>
-      <c r="E4" s="1"/>
       <c r="F4" s="1"/>
-    </row>
-    <row r="5" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="G4" s="1"/>
+    </row>
+    <row r="5" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A5" s="1"/>
       <c r="B5" s="1"/>
       <c r="C5" s="1"/>
-      <c r="D5" s="8" t="s">
+      <c r="D5" s="1"/>
+      <c r="E5" s="8" t="s">
         <v>39</v>
       </c>
-      <c r="E5" s="1"/>
       <c r="F5" s="1"/>
-    </row>
-    <row r="6" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="G5" s="1"/>
+    </row>
+    <row r="6" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A6" s="1">
         <v>2</v>
       </c>
@@ -1381,359 +1393,399 @@
         <v>5</v>
       </c>
       <c r="C6" s="1" t="s">
+        <v>94</v>
+      </c>
+      <c r="D6" s="1" t="s">
         <v>17</v>
       </c>
-      <c r="D6" s="3"/>
-      <c r="E6" s="1"/>
+      <c r="E6" s="3"/>
       <c r="F6" s="1"/>
-    </row>
-    <row r="7" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="G6" s="1"/>
+    </row>
+    <row r="7" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A7" s="1"/>
       <c r="B7" s="1"/>
       <c r="C7" s="1"/>
-      <c r="D7" s="3" t="s">
+      <c r="D7" s="1"/>
+      <c r="E7" s="3" t="s">
         <v>40</v>
       </c>
-      <c r="E7" s="1"/>
       <c r="F7" s="1"/>
-    </row>
-    <row r="8" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="G7" s="1"/>
+    </row>
+    <row r="8" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A8" s="1"/>
       <c r="B8" s="1"/>
       <c r="C8" s="1"/>
-      <c r="D8" s="3" t="s">
+      <c r="D8" s="1"/>
+      <c r="E8" s="3" t="s">
         <v>41</v>
       </c>
-      <c r="E8" s="1"/>
       <c r="F8" s="1"/>
-    </row>
-    <row r="9" spans="1:6" ht="50.4" x14ac:dyDescent="0.3">
+      <c r="G8" s="1"/>
+    </row>
+    <row r="9" spans="1:7" ht="50.4" x14ac:dyDescent="0.3">
       <c r="A9" s="1"/>
       <c r="B9" s="1"/>
       <c r="C9" s="1"/>
-      <c r="D9" s="8" t="s">
+      <c r="D9" s="1"/>
+      <c r="E9" s="8" t="s">
         <v>42</v>
       </c>
-      <c r="E9" s="1"/>
-      <c r="F9" s="4" t="s">
+      <c r="F9" s="1"/>
+      <c r="G9" s="4" t="s">
         <v>44</v>
       </c>
     </row>
-    <row r="10" spans="1:6" ht="50.4" x14ac:dyDescent="0.3">
+    <row r="10" spans="1:7" ht="50.4" x14ac:dyDescent="0.3">
       <c r="A10" s="1"/>
       <c r="B10" s="1"/>
       <c r="C10" s="1"/>
-      <c r="D10" s="8" t="s">
+      <c r="D10" s="1"/>
+      <c r="E10" s="8" t="s">
         <v>43</v>
       </c>
-      <c r="E10" s="1"/>
-      <c r="F10" s="4" t="s">
+      <c r="F10" s="1"/>
+      <c r="G10" s="4" t="s">
         <v>45</v>
       </c>
     </row>
-    <row r="11" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="11" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A11" s="1"/>
       <c r="B11" s="1"/>
       <c r="C11" s="1"/>
-      <c r="D11" s="8" t="s">
+      <c r="D11" s="1"/>
+      <c r="E11" s="8" t="s">
         <v>46</v>
       </c>
-      <c r="E11" s="1"/>
-      <c r="F11" s="4"/>
-    </row>
-    <row r="12" spans="1:6" ht="67.2" x14ac:dyDescent="0.3">
+      <c r="F11" s="1"/>
+      <c r="G11" s="4"/>
+    </row>
+    <row r="12" spans="1:7" ht="67.2" x14ac:dyDescent="0.3">
       <c r="A12" s="1"/>
       <c r="B12" s="1"/>
       <c r="C12" s="1"/>
-      <c r="D12" s="8" t="s">
+      <c r="D12" s="1"/>
+      <c r="E12" s="8" t="s">
         <v>47</v>
       </c>
-      <c r="E12" s="1"/>
-      <c r="F12" s="10" t="s">
+      <c r="F12" s="1"/>
+      <c r="G12" s="10" t="s">
         <v>48</v>
       </c>
     </row>
-    <row r="13" spans="1:6" ht="67.2" x14ac:dyDescent="0.3">
+    <row r="13" spans="1:7" ht="67.2" x14ac:dyDescent="0.3">
       <c r="A13" s="1"/>
       <c r="B13" s="1"/>
       <c r="C13" s="1"/>
-      <c r="D13" s="8" t="s">
+      <c r="D13" s="1"/>
+      <c r="E13" s="8" t="s">
         <v>49</v>
       </c>
-      <c r="E13" s="1"/>
-      <c r="F13" s="4" t="s">
+      <c r="F13" s="1"/>
+      <c r="G13" s="4" t="s">
         <v>51</v>
       </c>
     </row>
-    <row r="14" spans="1:6" ht="33.6" x14ac:dyDescent="0.3">
+    <row r="14" spans="1:7" ht="33.6" x14ac:dyDescent="0.3">
       <c r="A14" s="1"/>
       <c r="B14" s="1"/>
       <c r="C14" s="1"/>
-      <c r="D14" s="8" t="s">
+      <c r="D14" s="1"/>
+      <c r="E14" s="8" t="s">
         <v>50</v>
       </c>
-      <c r="E14" s="1"/>
-      <c r="F14" s="4" t="s">
+      <c r="F14" s="1"/>
+      <c r="G14" s="4" t="s">
         <v>52</v>
       </c>
     </row>
-    <row r="15" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="15" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A15" s="1"/>
       <c r="B15" s="1"/>
       <c r="C15" s="1"/>
-      <c r="D15" s="8" t="s">
+      <c r="D15" s="1"/>
+      <c r="E15" s="8" t="s">
         <v>53</v>
       </c>
-      <c r="E15" s="1"/>
-      <c r="F15" s="4"/>
-    </row>
-    <row r="16" spans="1:6" ht="50.4" x14ac:dyDescent="0.3">
+      <c r="F15" s="1"/>
+      <c r="G15" s="4"/>
+    </row>
+    <row r="16" spans="1:7" ht="50.4" x14ac:dyDescent="0.3">
       <c r="A16" s="1"/>
       <c r="B16" s="1"/>
       <c r="C16" s="1"/>
-      <c r="D16" s="8" t="s">
+      <c r="D16" s="1"/>
+      <c r="E16" s="8" t="s">
         <v>54</v>
       </c>
-      <c r="E16" s="1"/>
-      <c r="F16" s="4" t="s">
+      <c r="F16" s="1"/>
+      <c r="G16" s="4" t="s">
         <v>55</v>
       </c>
     </row>
-    <row r="17" spans="1:12" x14ac:dyDescent="0.3">
+    <row r="17" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A17" s="1"/>
       <c r="B17" s="1"/>
       <c r="C17" s="1"/>
-      <c r="D17" s="8" t="s">
+      <c r="D17" s="1"/>
+      <c r="E17" s="8" t="s">
         <v>56</v>
       </c>
-      <c r="E17" s="1"/>
-      <c r="F17" s="4"/>
-    </row>
-    <row r="18" spans="1:12" x14ac:dyDescent="0.3">
+      <c r="F17" s="1"/>
+      <c r="G17" s="4"/>
+    </row>
+    <row r="18" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A18" s="1"/>
       <c r="B18" s="1"/>
       <c r="C18" s="1"/>
-      <c r="D18" s="8" t="s">
+      <c r="D18" s="1"/>
+      <c r="E18" s="8" t="s">
         <v>58</v>
       </c>
-      <c r="E18" s="1"/>
-      <c r="F18" s="4" t="s">
+      <c r="F18" s="1"/>
+      <c r="G18" s="4" t="s">
         <v>59</v>
       </c>
     </row>
-    <row r="19" spans="1:12" ht="409.6" x14ac:dyDescent="0.3">
+    <row r="19" spans="1:13" ht="409.6" x14ac:dyDescent="0.3">
       <c r="A19" s="1">
         <v>3</v>
       </c>
       <c r="B19" s="1" t="s">
         <v>24</v>
       </c>
-      <c r="C19" s="1"/>
-      <c r="D19" s="9" t="s">
+      <c r="C19" s="1" t="s">
+        <v>94</v>
+      </c>
+      <c r="D19" s="1"/>
+      <c r="E19" s="9" t="s">
         <v>34</v>
       </c>
-      <c r="E19" s="1"/>
-      <c r="F19" s="4" t="s">
+      <c r="F19" s="1"/>
+      <c r="G19" s="4" t="s">
         <v>36</v>
       </c>
-      <c r="G19" s="7" t="s">
+      <c r="H19" s="7" t="s">
         <v>28</v>
       </c>
-      <c r="H19" s="7" t="s">
+      <c r="I19" s="7" t="s">
         <v>29</v>
       </c>
-      <c r="I19" s="7" t="s">
+      <c r="J19" s="7" t="s">
         <v>30</v>
       </c>
-      <c r="J19" s="7" t="s">
+      <c r="K19" s="7" t="s">
         <v>31</v>
       </c>
-      <c r="K19" s="7" t="s">
+      <c r="L19" s="7" t="s">
         <v>32</v>
       </c>
-      <c r="L19" s="7" t="s">
+      <c r="M19" s="7" t="s">
         <v>33</v>
       </c>
     </row>
-    <row r="20" spans="1:12" ht="100.8" x14ac:dyDescent="0.3">
+    <row r="20" spans="1:13" ht="100.8" x14ac:dyDescent="0.3">
       <c r="A20" s="1"/>
       <c r="B20" s="1"/>
       <c r="C20" s="1"/>
-      <c r="D20" s="8"/>
-      <c r="E20" s="1"/>
-      <c r="F20" s="4" t="s">
+      <c r="D20" s="1"/>
+      <c r="E20" s="8"/>
+      <c r="F20" s="1"/>
+      <c r="G20" s="4" t="s">
         <v>35</v>
       </c>
-      <c r="G20" s="7"/>
       <c r="H20" s="7"/>
       <c r="I20" s="7"/>
       <c r="J20" s="7"/>
       <c r="K20" s="7"/>
       <c r="L20" s="7"/>
-    </row>
-    <row r="21" spans="1:12" ht="346.2" x14ac:dyDescent="0.3">
+      <c r="M20" s="7"/>
+    </row>
+    <row r="21" spans="1:13" ht="363" x14ac:dyDescent="0.3">
       <c r="A21" s="1">
         <v>4</v>
       </c>
       <c r="B21" s="1" t="s">
         <v>25</v>
       </c>
-      <c r="C21" s="1"/>
-      <c r="D21" s="8" t="s">
+      <c r="C21" s="1" t="s">
+        <v>94</v>
+      </c>
+      <c r="D21" s="1"/>
+      <c r="E21" s="8" t="s">
         <v>60</v>
       </c>
-      <c r="E21" s="1"/>
-      <c r="F21" s="4" t="s">
+      <c r="F21" s="1"/>
+      <c r="G21" s="4" t="s">
         <v>91</v>
       </c>
     </row>
-    <row r="22" spans="1:12" ht="67.2" x14ac:dyDescent="0.3">
+    <row r="22" spans="1:13" ht="67.2" x14ac:dyDescent="0.3">
       <c r="A22" s="1"/>
       <c r="B22" s="1"/>
       <c r="C22" s="1"/>
-      <c r="D22" s="8" t="s">
+      <c r="D22" s="1"/>
+      <c r="E22" s="8" t="s">
         <v>61</v>
       </c>
-      <c r="E22" s="1"/>
-      <c r="F22" s="12" t="s">
+      <c r="F22" s="1"/>
+      <c r="G22" s="12" t="s">
         <v>92</v>
       </c>
     </row>
-    <row r="23" spans="1:12" ht="67.2" x14ac:dyDescent="0.3">
+    <row r="23" spans="1:13" ht="134.4" x14ac:dyDescent="0.3">
       <c r="A23" s="1"/>
       <c r="B23" s="1"/>
       <c r="C23" s="1"/>
-      <c r="D23" s="8" t="s">
+      <c r="D23" s="1"/>
+      <c r="E23" s="8" t="s">
         <v>62</v>
       </c>
-      <c r="E23" s="1"/>
-      <c r="F23" s="4" t="s">
+      <c r="F23" s="1"/>
+      <c r="G23" s="4" t="s">
         <v>93</v>
       </c>
     </row>
-    <row r="24" spans="1:12" x14ac:dyDescent="0.3">
+    <row r="24" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A24" s="1">
         <v>5</v>
       </c>
       <c r="B24" s="1" t="s">
         <v>26</v>
       </c>
-      <c r="C24" s="1"/>
-      <c r="D24" s="8"/>
-      <c r="E24" s="1"/>
+      <c r="C24" s="1" t="s">
+        <v>94</v>
+      </c>
+      <c r="D24" s="1"/>
+      <c r="E24" s="8"/>
       <c r="F24" s="1"/>
-    </row>
-    <row r="25" spans="1:12" x14ac:dyDescent="0.3">
+      <c r="G24" s="1"/>
+    </row>
+    <row r="25" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A25" s="1"/>
       <c r="B25" s="1"/>
       <c r="C25" s="1"/>
-      <c r="D25" s="11" t="s">
+      <c r="D25" s="1"/>
+      <c r="E25" s="11" t="s">
         <v>57</v>
       </c>
-      <c r="E25" s="1"/>
       <c r="F25" s="1"/>
-    </row>
-    <row r="26" spans="1:12" x14ac:dyDescent="0.3">
+      <c r="G25" s="1"/>
+    </row>
+    <row r="26" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A26" s="1"/>
       <c r="B26" s="1"/>
       <c r="C26" s="1"/>
-      <c r="D26" s="8" t="s">
+      <c r="D26" s="1"/>
+      <c r="E26" s="8" t="s">
         <v>63</v>
       </c>
-      <c r="E26" s="1"/>
       <c r="F26" s="1"/>
-    </row>
-    <row r="27" spans="1:12" x14ac:dyDescent="0.3">
+      <c r="G26" s="1"/>
+    </row>
+    <row r="27" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A27" s="1"/>
       <c r="B27" s="1"/>
       <c r="C27" s="1"/>
-      <c r="D27" s="11" t="s">
+      <c r="D27" s="1"/>
+      <c r="E27" s="11" t="s">
         <v>64</v>
       </c>
-      <c r="E27" s="1"/>
       <c r="F27" s="1"/>
-    </row>
-    <row r="28" spans="1:12" x14ac:dyDescent="0.3">
+      <c r="G27" s="1"/>
+    </row>
+    <row r="28" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A28" s="1">
         <v>6</v>
       </c>
       <c r="B28" s="1" t="s">
         <v>27</v>
       </c>
-      <c r="C28" s="1"/>
-      <c r="D28" s="3"/>
-      <c r="E28" s="1"/>
+      <c r="C28" s="1" t="s">
+        <v>94</v>
+      </c>
+      <c r="D28" s="1"/>
+      <c r="E28" s="3"/>
       <c r="F28" s="1"/>
-    </row>
-    <row r="29" spans="1:12" x14ac:dyDescent="0.3">
+      <c r="G28" s="1"/>
+    </row>
+    <row r="29" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A29" s="1"/>
       <c r="B29" s="1"/>
       <c r="C29" s="1"/>
-      <c r="D29" s="8" t="s">
+      <c r="D29" s="1"/>
+      <c r="E29" s="8" t="s">
         <v>65</v>
       </c>
-      <c r="E29" s="1"/>
       <c r="F29" s="1"/>
-    </row>
-    <row r="30" spans="1:12" x14ac:dyDescent="0.3">
+      <c r="G29" s="1"/>
+    </row>
+    <row r="30" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A30" s="1"/>
       <c r="B30" s="1"/>
       <c r="C30" s="1"/>
-      <c r="D30" s="8" t="s">
+      <c r="D30" s="1"/>
+      <c r="E30" s="8" t="s">
         <v>66</v>
       </c>
-      <c r="E30" s="1"/>
       <c r="F30" s="1"/>
-    </row>
-    <row r="31" spans="1:12" x14ac:dyDescent="0.3">
+      <c r="G30" s="1"/>
+    </row>
+    <row r="31" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A31" s="1"/>
       <c r="B31" s="1"/>
       <c r="C31" s="1"/>
-      <c r="D31" s="8" t="s">
+      <c r="D31" s="1"/>
+      <c r="E31" s="8" t="s">
         <v>67</v>
       </c>
-      <c r="E31" s="1"/>
       <c r="F31" s="1"/>
-    </row>
-    <row r="32" spans="1:12" x14ac:dyDescent="0.3">
+      <c r="G31" s="1"/>
+    </row>
+    <row r="32" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A32" s="1">
         <v>7</v>
       </c>
       <c r="B32" s="1" t="s">
         <v>18</v>
       </c>
-      <c r="C32" s="1" t="s">
+      <c r="C32" s="1"/>
+      <c r="D32" s="1" t="s">
         <v>19</v>
       </c>
-      <c r="D32" s="3"/>
-      <c r="E32" s="1"/>
+      <c r="E32" s="3"/>
       <c r="F32" s="1"/>
-    </row>
-    <row r="33" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="G32" s="1"/>
+    </row>
+    <row r="33" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A33" s="1"/>
       <c r="B33" s="1"/>
       <c r="C33" s="1"/>
-      <c r="D33" s="3"/>
-      <c r="E33" s="1"/>
+      <c r="D33" s="1"/>
+      <c r="E33" s="3"/>
       <c r="F33" s="1"/>
-    </row>
-    <row r="34" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="G33" s="1"/>
+    </row>
+    <row r="34" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A34" s="1"/>
       <c r="B34" s="1"/>
       <c r="C34" s="1"/>
-      <c r="D34" s="3"/>
-      <c r="E34" s="1"/>
+      <c r="D34" s="1"/>
+      <c r="E34" s="3"/>
       <c r="F34" s="1"/>
-    </row>
-    <row r="35" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="G34" s="1"/>
+    </row>
+    <row r="35" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A35" s="1"/>
       <c r="B35" s="1"/>
       <c r="C35" s="1"/>
-      <c r="D35" s="3"/>
-      <c r="E35" s="1"/>
+      <c r="D35" s="1"/>
+      <c r="E35" s="3"/>
       <c r="F35" s="1"/>
-    </row>
-    <row r="36" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="G35" s="1"/>
+    </row>
+    <row r="36" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A36" s="1">
         <v>8</v>
       </c>
@@ -1741,41 +1793,45 @@
         <v>20</v>
       </c>
       <c r="C36" s="1"/>
-      <c r="D36" s="3"/>
-      <c r="E36" s="1"/>
-      <c r="F36" s="4"/>
-    </row>
-    <row r="37" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="D36" s="1"/>
+      <c r="E36" s="3"/>
+      <c r="F36" s="1"/>
+      <c r="G36" s="4"/>
+    </row>
+    <row r="37" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A37" s="1"/>
       <c r="B37" s="1"/>
       <c r="C37" s="1"/>
-      <c r="D37" s="8" t="s">
+      <c r="D37" s="1"/>
+      <c r="E37" s="8" t="s">
         <v>68</v>
       </c>
-      <c r="E37" s="1"/>
-      <c r="F37" s="4"/>
-    </row>
-    <row r="38" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="F37" s="1"/>
+      <c r="G37" s="4"/>
+    </row>
+    <row r="38" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A38" s="1"/>
       <c r="B38" s="1"/>
       <c r="C38" s="1"/>
-      <c r="D38" s="8" t="s">
+      <c r="D38" s="1"/>
+      <c r="E38" s="8" t="s">
         <v>68</v>
       </c>
-      <c r="E38" s="1"/>
-      <c r="F38" s="4"/>
-    </row>
-    <row r="39" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="F38" s="1"/>
+      <c r="G38" s="4"/>
+    </row>
+    <row r="39" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A39" s="1"/>
       <c r="B39" s="1"/>
       <c r="C39" s="1"/>
-      <c r="D39" s="8" t="s">
+      <c r="D39" s="1"/>
+      <c r="E39" s="8" t="s">
         <v>69</v>
       </c>
-      <c r="E39" s="1"/>
-      <c r="F39" s="4"/>
-    </row>
-    <row r="40" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="F39" s="1"/>
+      <c r="G39" s="4"/>
+    </row>
+    <row r="40" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A40" s="1">
         <v>9</v>
       </c>
@@ -1783,338 +1839,378 @@
         <v>6</v>
       </c>
       <c r="C40" s="1"/>
-      <c r="D40" s="3"/>
-      <c r="E40" s="1"/>
+      <c r="D40" s="1"/>
+      <c r="E40" s="3"/>
       <c r="F40" s="1"/>
-    </row>
-    <row r="41" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="G40" s="1"/>
+    </row>
+    <row r="41" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A41" s="1"/>
       <c r="B41" s="1"/>
       <c r="C41" s="1"/>
-      <c r="D41" s="8" t="s">
+      <c r="D41" s="1"/>
+      <c r="E41" s="8" t="s">
         <v>70</v>
       </c>
-      <c r="E41" s="1"/>
       <c r="F41" s="1"/>
-    </row>
-    <row r="42" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="G41" s="1"/>
+    </row>
+    <row r="42" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A42" s="1"/>
       <c r="B42" s="1"/>
       <c r="C42" s="1"/>
-      <c r="D42" s="11" t="s">
+      <c r="D42" s="1"/>
+      <c r="E42" s="11" t="s">
         <v>71</v>
       </c>
-      <c r="E42" s="1"/>
       <c r="F42" s="1"/>
-    </row>
-    <row r="43" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="G42" s="1"/>
+    </row>
+    <row r="43" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A43" s="1"/>
       <c r="B43" s="1"/>
       <c r="C43" s="1"/>
-      <c r="D43" s="8" t="s">
+      <c r="D43" s="1"/>
+      <c r="E43" s="8" t="s">
         <v>72</v>
       </c>
-      <c r="E43" s="1"/>
       <c r="F43" s="1"/>
-    </row>
-    <row r="44" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="G43" s="1"/>
+    </row>
+    <row r="44" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A44" s="1">
         <v>10</v>
       </c>
       <c r="B44" s="1" t="s">
         <v>7</v>
       </c>
-      <c r="C44" s="1"/>
-      <c r="D44" s="3"/>
-      <c r="E44" s="1"/>
+      <c r="C44" s="1" t="s">
+        <v>94</v>
+      </c>
+      <c r="D44" s="1"/>
+      <c r="E44" s="3"/>
       <c r="F44" s="1"/>
-    </row>
-    <row r="45" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="G44" s="1"/>
+    </row>
+    <row r="45" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A45" s="1"/>
       <c r="B45" s="1"/>
       <c r="C45" s="1"/>
-      <c r="D45" s="8" t="s">
+      <c r="D45" s="1"/>
+      <c r="E45" s="8" t="s">
         <v>73</v>
       </c>
-      <c r="E45" s="1"/>
       <c r="F45" s="1"/>
-    </row>
-    <row r="46" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="G45" s="1"/>
+    </row>
+    <row r="46" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A46" s="1"/>
       <c r="B46" s="1"/>
       <c r="C46" s="1"/>
-      <c r="D46" s="8" t="s">
+      <c r="D46" s="1"/>
+      <c r="E46" s="8" t="s">
         <v>74</v>
       </c>
-      <c r="E46" s="1"/>
       <c r="F46" s="1"/>
-    </row>
-    <row r="47" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="G46" s="1"/>
+    </row>
+    <row r="47" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A47" s="1"/>
       <c r="B47" s="1"/>
       <c r="C47" s="1"/>
-      <c r="D47" s="8" t="s">
+      <c r="D47" s="1"/>
+      <c r="E47" s="8" t="s">
         <v>75</v>
       </c>
-      <c r="E47" s="1"/>
       <c r="F47" s="1"/>
-    </row>
-    <row r="48" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="G47" s="1"/>
+    </row>
+    <row r="48" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A48" s="1">
         <v>11</v>
       </c>
       <c r="B48" s="1" t="s">
         <v>21</v>
       </c>
-      <c r="C48" s="1"/>
-      <c r="D48" s="3"/>
-      <c r="E48" s="1"/>
+      <c r="C48" s="1" t="s">
+        <v>94</v>
+      </c>
+      <c r="D48" s="1"/>
+      <c r="E48" s="3"/>
       <c r="F48" s="1"/>
-    </row>
-    <row r="49" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="G48" s="1"/>
+    </row>
+    <row r="49" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A49" s="1"/>
       <c r="B49" s="1"/>
       <c r="C49" s="1"/>
-      <c r="D49" s="8" t="s">
+      <c r="D49" s="1"/>
+      <c r="E49" s="8" t="s">
         <v>76</v>
       </c>
-      <c r="E49" s="1"/>
       <c r="F49" s="1"/>
-    </row>
-    <row r="50" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="G49" s="1"/>
+    </row>
+    <row r="50" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A50" s="1"/>
       <c r="B50" s="1"/>
       <c r="C50" s="1"/>
-      <c r="D50" s="8" t="s">
+      <c r="D50" s="1"/>
+      <c r="E50" s="8" t="s">
         <v>77</v>
       </c>
-      <c r="E50" s="1"/>
       <c r="F50" s="1"/>
-    </row>
-    <row r="51" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="G50" s="1"/>
+    </row>
+    <row r="51" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A51" s="1"/>
       <c r="B51" s="1"/>
       <c r="C51" s="1"/>
-      <c r="D51" s="8" t="s">
+      <c r="D51" s="1"/>
+      <c r="E51" s="8" t="s">
         <v>78</v>
       </c>
-      <c r="E51" s="1"/>
       <c r="F51" s="1"/>
-    </row>
-    <row r="52" spans="1:6" ht="16.2" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="G51" s="1"/>
+    </row>
+    <row r="52" spans="1:7" ht="16.2" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A52" s="1">
         <v>12</v>
       </c>
       <c r="B52" s="1" t="s">
         <v>8</v>
       </c>
-      <c r="C52" s="1"/>
+      <c r="C52" s="1" t="s">
+        <v>94</v>
+      </c>
       <c r="D52" s="1"/>
       <c r="E52" s="1"/>
       <c r="F52" s="1"/>
-    </row>
-    <row r="53" spans="1:6" ht="16.2" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="G52" s="1"/>
+    </row>
+    <row r="53" spans="1:7" ht="16.2" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A53" s="1"/>
       <c r="B53" s="1"/>
       <c r="C53" s="1"/>
-      <c r="D53" s="8" t="s">
+      <c r="D53" s="1"/>
+      <c r="E53" s="8" t="s">
         <v>79</v>
       </c>
-      <c r="E53" s="1"/>
       <c r="F53" s="1"/>
-    </row>
-    <row r="54" spans="1:6" ht="43.2" x14ac:dyDescent="0.3">
+      <c r="G53" s="1"/>
+    </row>
+    <row r="54" spans="1:7" ht="43.2" x14ac:dyDescent="0.3">
       <c r="A54" s="1"/>
       <c r="B54" s="1"/>
       <c r="C54" s="1"/>
-      <c r="D54" s="9" t="s">
+      <c r="D54" s="1"/>
+      <c r="E54" s="9" t="s">
         <v>80</v>
       </c>
-      <c r="E54" s="1"/>
       <c r="F54" s="1"/>
-    </row>
-    <row r="55" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="G54" s="1"/>
+    </row>
+    <row r="55" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A55" s="1"/>
       <c r="B55" s="1"/>
       <c r="C55" s="1"/>
-      <c r="D55" s="8" t="s">
+      <c r="D55" s="1"/>
+      <c r="E55" s="8" t="s">
         <v>81</v>
       </c>
-      <c r="E55" s="1"/>
       <c r="F55" s="1"/>
-    </row>
-    <row r="56" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="G55" s="1"/>
+    </row>
+    <row r="56" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A56" s="1">
         <v>13</v>
       </c>
       <c r="B56" s="1" t="s">
         <v>9</v>
       </c>
-      <c r="C56" s="1"/>
+      <c r="C56" s="1" t="s">
+        <v>94</v>
+      </c>
       <c r="D56" s="1"/>
       <c r="E56" s="1"/>
       <c r="F56" s="1"/>
-    </row>
-    <row r="57" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="G56" s="1"/>
+    </row>
+    <row r="57" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A57" s="1"/>
       <c r="B57" s="1"/>
       <c r="C57" s="1"/>
-      <c r="D57" s="8" t="s">
+      <c r="D57" s="1"/>
+      <c r="E57" s="8" t="s">
         <v>82</v>
       </c>
-      <c r="E57" s="1"/>
       <c r="F57" s="1"/>
-    </row>
-    <row r="58" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="G57" s="1"/>
+    </row>
+    <row r="58" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A58" s="1"/>
       <c r="B58" s="1"/>
       <c r="C58" s="1"/>
-      <c r="D58" s="8" t="s">
+      <c r="D58" s="1"/>
+      <c r="E58" s="8" t="s">
         <v>83</v>
       </c>
-      <c r="E58" s="1"/>
       <c r="F58" s="1"/>
-    </row>
-    <row r="59" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="G58" s="1"/>
+    </row>
+    <row r="59" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A59" s="1"/>
       <c r="B59" s="1"/>
       <c r="C59" s="1"/>
-      <c r="D59" s="8" t="s">
+      <c r="D59" s="1"/>
+      <c r="E59" s="8" t="s">
         <v>84</v>
       </c>
-      <c r="E59" s="1"/>
       <c r="F59" s="1"/>
-    </row>
-    <row r="60" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="G59" s="1"/>
+    </row>
+    <row r="60" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A60" s="1">
         <v>14</v>
       </c>
       <c r="B60" s="1" t="s">
         <v>10</v>
       </c>
-      <c r="C60" s="1"/>
+      <c r="C60" s="1" t="s">
+        <v>94</v>
+      </c>
       <c r="D60" s="1"/>
       <c r="E60" s="1"/>
       <c r="F60" s="1"/>
-    </row>
-    <row r="61" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="G60" s="1"/>
+    </row>
+    <row r="61" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A61" s="1"/>
       <c r="B61" s="1"/>
       <c r="C61" s="1"/>
-      <c r="D61" s="8" t="s">
+      <c r="D61" s="1"/>
+      <c r="E61" s="8" t="s">
         <v>85</v>
       </c>
-      <c r="E61" s="1"/>
       <c r="F61" s="1"/>
-    </row>
-    <row r="62" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="G61" s="1"/>
+    </row>
+    <row r="62" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A62" s="1"/>
       <c r="B62" s="1"/>
       <c r="C62" s="1"/>
-      <c r="D62" s="8" t="s">
+      <c r="D62" s="1"/>
+      <c r="E62" s="8" t="s">
         <v>86</v>
       </c>
-      <c r="E62" s="1"/>
       <c r="F62" s="1"/>
-    </row>
-    <row r="63" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="G62" s="1"/>
+    </row>
+    <row r="63" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A63" s="1"/>
       <c r="B63" s="1"/>
       <c r="C63" s="1"/>
-      <c r="D63" s="8" t="s">
+      <c r="D63" s="1"/>
+      <c r="E63" s="8" t="s">
         <v>87</v>
       </c>
-      <c r="E63" s="1"/>
       <c r="F63" s="1"/>
-    </row>
-    <row r="64" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="G63" s="1"/>
+    </row>
+    <row r="64" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A64" s="1">
         <v>18</v>
       </c>
       <c r="B64" s="1" t="s">
         <v>11</v>
       </c>
-      <c r="C64" s="1"/>
-      <c r="E64" s="1"/>
+      <c r="C64" s="1" t="s">
+        <v>94</v>
+      </c>
+      <c r="D64" s="1"/>
       <c r="F64" s="1"/>
-    </row>
-    <row r="65" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="G64" s="1"/>
+    </row>
+    <row r="65" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A65" s="1"/>
       <c r="B65" s="1"/>
       <c r="C65" s="1"/>
-      <c r="D65" s="8" t="s">
+      <c r="D65" s="1"/>
+      <c r="E65" s="8" t="s">
         <v>88</v>
       </c>
-      <c r="E65" s="1"/>
       <c r="F65" s="1"/>
-    </row>
-    <row r="66" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="G65" s="1"/>
+    </row>
+    <row r="66" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A66" s="1"/>
       <c r="B66" s="1"/>
       <c r="C66" s="1"/>
-      <c r="D66" s="8" t="s">
+      <c r="D66" s="1"/>
+      <c r="E66" s="8" t="s">
         <v>89</v>
       </c>
-      <c r="E66" s="1"/>
       <c r="F66" s="1"/>
-    </row>
-    <row r="67" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="G66" s="1"/>
+    </row>
+    <row r="67" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A67" s="1"/>
       <c r="B67" s="1"/>
       <c r="C67" s="1"/>
-      <c r="D67" s="8" t="s">
+      <c r="D67" s="1"/>
+      <c r="E67" s="8" t="s">
         <v>90</v>
       </c>
-      <c r="E67" s="1"/>
       <c r="F67" s="1"/>
+      <c r="G67" s="1"/>
     </row>
   </sheetData>
   <hyperlinks>
-    <hyperlink ref="D19" r:id="rId1" xr:uid="{1A58C001-5CA8-4698-80C0-8E9AE993DCFE}"/>
-    <hyperlink ref="D3" r:id="rId2" xr:uid="{CBEFF935-43B0-4678-9E84-68B644F90B2F}"/>
-    <hyperlink ref="D4" r:id="rId3" xr:uid="{633A55FD-AC9E-4CC7-9C45-F483B7B86CC6}"/>
-    <hyperlink ref="D5" r:id="rId4" xr:uid="{C376D87F-A4F7-4EBA-9E54-34E9C25C3A82}"/>
-    <hyperlink ref="D9" r:id="rId5" xr:uid="{3D4CDB3D-FD7D-4C96-A284-D41AD758067D}"/>
-    <hyperlink ref="D10" r:id="rId6" xr:uid="{6E67B1FB-A93C-4545-8E38-61C200CB2B2B}"/>
-    <hyperlink ref="D12" r:id="rId7" xr:uid="{F3F87AC7-D2DF-4FC2-A558-288F3C41852C}"/>
-    <hyperlink ref="D13" r:id="rId8" xr:uid="{DC1A27B0-76E1-46DA-8229-EE5213A97D5A}"/>
-    <hyperlink ref="D14" r:id="rId9" xr:uid="{538E1B02-D115-4BE0-B10B-C4155EEB2BA3}"/>
-    <hyperlink ref="D16" r:id="rId10" xr:uid="{F41F0039-D81A-4C99-8C16-55823C8410C4}"/>
-    <hyperlink ref="D17" r:id="rId11" xr:uid="{83CCC76D-FE94-4FC4-BF27-CFE9109A671F}"/>
-    <hyperlink ref="D18" r:id="rId12" xr:uid="{7E79A88D-4206-4763-A8D4-74CAFB94C7D7}"/>
-    <hyperlink ref="D21" r:id="rId13" xr:uid="{ED86CCA8-0EAD-491F-AA9E-FA3C5C488EA3}"/>
-    <hyperlink ref="D22" r:id="rId14" xr:uid="{17B39EB6-358C-480D-909B-37DAB741C407}"/>
-    <hyperlink ref="D23" r:id="rId15" xr:uid="{5951153B-15DB-4D2D-B42F-B7342FB517A9}"/>
-    <hyperlink ref="D25" r:id="rId16" xr:uid="{E5858E9F-8347-40E4-AB68-FDC60759EEE0}"/>
-    <hyperlink ref="D26" r:id="rId17" xr:uid="{9A46811D-9BC9-45FB-BE9A-6C9AAE3B0B8A}"/>
-    <hyperlink ref="D27" r:id="rId18" xr:uid="{8886B4E4-E47E-4AFA-84B2-98EC5C0446AE}"/>
-    <hyperlink ref="D29" r:id="rId19" xr:uid="{20AF3F9E-8477-4D5A-8A6F-5543FDF4707C}"/>
-    <hyperlink ref="D30" r:id="rId20" xr:uid="{B0AD597E-0EA7-41D4-A4D7-E9EF74B7A734}"/>
-    <hyperlink ref="D31" r:id="rId21" xr:uid="{F5F2B4AD-B15D-4C92-A1EA-A57127911B9D}"/>
-    <hyperlink ref="D37" r:id="rId22" xr:uid="{4624F232-3D34-48DC-B415-7CECCADC42B8}"/>
-    <hyperlink ref="D38" r:id="rId23" xr:uid="{A4A6056C-13F1-465A-B54A-2281951CD475}"/>
-    <hyperlink ref="D39" r:id="rId24" xr:uid="{BFA899E4-939B-43CC-82B6-1D70058F8977}"/>
-    <hyperlink ref="D41" r:id="rId25" xr:uid="{2A075F6E-1EE1-474C-8E56-C65551051CA4}"/>
-    <hyperlink ref="D42" r:id="rId26" xr:uid="{B5D1459A-5F0F-4959-A99E-C4E39D53D64B}"/>
-    <hyperlink ref="D43" r:id="rId27" xr:uid="{DCE145DC-0FDF-4700-8929-6CF19C89DD5D}"/>
-    <hyperlink ref="D45" r:id="rId28" xr:uid="{60E5CF1B-4F4B-4488-9935-6D81F8E339EB}"/>
-    <hyperlink ref="D46" r:id="rId29" xr:uid="{A0FE471F-1C7C-4FB9-B7EF-50EC473AABD6}"/>
-    <hyperlink ref="D47" r:id="rId30" xr:uid="{154285D1-D400-4BD4-9DDB-4727FB3E5293}"/>
-    <hyperlink ref="D49" r:id="rId31" xr:uid="{812D3FEE-6E5E-4F47-A8F5-AE68E5657B67}"/>
-    <hyperlink ref="D50" r:id="rId32" xr:uid="{C6A20CB6-75D4-4709-A8B7-BE33D4151F28}"/>
-    <hyperlink ref="D51" r:id="rId33" xr:uid="{9481162F-6F82-4DFA-B0C2-E18BB687952D}"/>
-    <hyperlink ref="D53" r:id="rId34" xr:uid="{CFD02D36-72A8-42B1-A4DE-1C9C2D861C73}"/>
-    <hyperlink ref="D54" r:id="rId35" display="https://github.com/nandland/spi-master.git" xr:uid="{53416F16-2477-4686-8E87-A8AD8D7CCC1F}"/>
-    <hyperlink ref="D55" r:id="rId36" xr:uid="{A99AFE91-E40C-499F-A378-DB0E4A9752C6}"/>
-    <hyperlink ref="D57" r:id="rId37" xr:uid="{4A875C94-4153-46A6-A61F-36FE74223FE7}"/>
-    <hyperlink ref="D58" r:id="rId38" xr:uid="{2ED8102E-B72A-4D1E-A759-58E935F46969}"/>
-    <hyperlink ref="D59" r:id="rId39" xr:uid="{DFBBC5CD-3D9D-418E-8066-231683E4BDF4}"/>
-    <hyperlink ref="D61" r:id="rId40" xr:uid="{7DC12D53-CADF-41F0-84FA-EC3FEF8D2B09}"/>
-    <hyperlink ref="D62" r:id="rId41" xr:uid="{E6D5499C-381E-4F21-AC15-85498A547D9F}"/>
-    <hyperlink ref="D63" r:id="rId42" xr:uid="{23D43F97-F3BD-4B09-B054-21598B4266EC}"/>
-    <hyperlink ref="D65" r:id="rId43" xr:uid="{17E1119E-5558-4FBE-8345-09B1C036E379}"/>
-    <hyperlink ref="D66" r:id="rId44" xr:uid="{6C304B39-61E6-4B75-9A64-ECE8CBB3A738}"/>
-    <hyperlink ref="D67" r:id="rId45" xr:uid="{BE0F3DB2-2E1A-4DB0-94E3-DFA902B71F20}"/>
+    <hyperlink ref="E19" r:id="rId1" xr:uid="{1A58C001-5CA8-4698-80C0-8E9AE993DCFE}"/>
+    <hyperlink ref="E3" r:id="rId2" xr:uid="{CBEFF935-43B0-4678-9E84-68B644F90B2F}"/>
+    <hyperlink ref="E4" r:id="rId3" xr:uid="{633A55FD-AC9E-4CC7-9C45-F483B7B86CC6}"/>
+    <hyperlink ref="E5" r:id="rId4" xr:uid="{C376D87F-A4F7-4EBA-9E54-34E9C25C3A82}"/>
+    <hyperlink ref="E9" r:id="rId5" xr:uid="{3D4CDB3D-FD7D-4C96-A284-D41AD758067D}"/>
+    <hyperlink ref="E10" r:id="rId6" xr:uid="{6E67B1FB-A93C-4545-8E38-61C200CB2B2B}"/>
+    <hyperlink ref="E12" r:id="rId7" xr:uid="{F3F87AC7-D2DF-4FC2-A558-288F3C41852C}"/>
+    <hyperlink ref="E13" r:id="rId8" xr:uid="{DC1A27B0-76E1-46DA-8229-EE5213A97D5A}"/>
+    <hyperlink ref="E14" r:id="rId9" xr:uid="{538E1B02-D115-4BE0-B10B-C4155EEB2BA3}"/>
+    <hyperlink ref="E16" r:id="rId10" xr:uid="{F41F0039-D81A-4C99-8C16-55823C8410C4}"/>
+    <hyperlink ref="E17" r:id="rId11" xr:uid="{83CCC76D-FE94-4FC4-BF27-CFE9109A671F}"/>
+    <hyperlink ref="E18" r:id="rId12" xr:uid="{7E79A88D-4206-4763-A8D4-74CAFB94C7D7}"/>
+    <hyperlink ref="E21" r:id="rId13" xr:uid="{ED86CCA8-0EAD-491F-AA9E-FA3C5C488EA3}"/>
+    <hyperlink ref="E22" r:id="rId14" xr:uid="{17B39EB6-358C-480D-909B-37DAB741C407}"/>
+    <hyperlink ref="E23" r:id="rId15" xr:uid="{5951153B-15DB-4D2D-B42F-B7342FB517A9}"/>
+    <hyperlink ref="E25" r:id="rId16" xr:uid="{E5858E9F-8347-40E4-AB68-FDC60759EEE0}"/>
+    <hyperlink ref="E26" r:id="rId17" xr:uid="{9A46811D-9BC9-45FB-BE9A-6C9AAE3B0B8A}"/>
+    <hyperlink ref="E27" r:id="rId18" xr:uid="{8886B4E4-E47E-4AFA-84B2-98EC5C0446AE}"/>
+    <hyperlink ref="E29" r:id="rId19" xr:uid="{20AF3F9E-8477-4D5A-8A6F-5543FDF4707C}"/>
+    <hyperlink ref="E30" r:id="rId20" xr:uid="{B0AD597E-0EA7-41D4-A4D7-E9EF74B7A734}"/>
+    <hyperlink ref="E31" r:id="rId21" xr:uid="{F5F2B4AD-B15D-4C92-A1EA-A57127911B9D}"/>
+    <hyperlink ref="E37" r:id="rId22" xr:uid="{4624F232-3D34-48DC-B415-7CECCADC42B8}"/>
+    <hyperlink ref="E38" r:id="rId23" xr:uid="{A4A6056C-13F1-465A-B54A-2281951CD475}"/>
+    <hyperlink ref="E39" r:id="rId24" xr:uid="{BFA899E4-939B-43CC-82B6-1D70058F8977}"/>
+    <hyperlink ref="E41" r:id="rId25" xr:uid="{2A075F6E-1EE1-474C-8E56-C65551051CA4}"/>
+    <hyperlink ref="E42" r:id="rId26" xr:uid="{B5D1459A-5F0F-4959-A99E-C4E39D53D64B}"/>
+    <hyperlink ref="E43" r:id="rId27" xr:uid="{DCE145DC-0FDF-4700-8929-6CF19C89DD5D}"/>
+    <hyperlink ref="E45" r:id="rId28" xr:uid="{60E5CF1B-4F4B-4488-9935-6D81F8E339EB}"/>
+    <hyperlink ref="E46" r:id="rId29" xr:uid="{A0FE471F-1C7C-4FB9-B7EF-50EC473AABD6}"/>
+    <hyperlink ref="E47" r:id="rId30" xr:uid="{154285D1-D400-4BD4-9DDB-4727FB3E5293}"/>
+    <hyperlink ref="E49" r:id="rId31" xr:uid="{812D3FEE-6E5E-4F47-A8F5-AE68E5657B67}"/>
+    <hyperlink ref="E50" r:id="rId32" xr:uid="{C6A20CB6-75D4-4709-A8B7-BE33D4151F28}"/>
+    <hyperlink ref="E51" r:id="rId33" xr:uid="{9481162F-6F82-4DFA-B0C2-E18BB687952D}"/>
+    <hyperlink ref="E53" r:id="rId34" xr:uid="{CFD02D36-72A8-42B1-A4DE-1C9C2D861C73}"/>
+    <hyperlink ref="E54" r:id="rId35" display="https://github.com/nandland/spi-master.git" xr:uid="{53416F16-2477-4686-8E87-A8AD8D7CCC1F}"/>
+    <hyperlink ref="E55" r:id="rId36" xr:uid="{A99AFE91-E40C-499F-A378-DB0E4A9752C6}"/>
+    <hyperlink ref="E57" r:id="rId37" xr:uid="{4A875C94-4153-46A6-A61F-36FE74223FE7}"/>
+    <hyperlink ref="E58" r:id="rId38" xr:uid="{2ED8102E-B72A-4D1E-A759-58E935F46969}"/>
+    <hyperlink ref="E59" r:id="rId39" xr:uid="{DFBBC5CD-3D9D-418E-8066-231683E4BDF4}"/>
+    <hyperlink ref="E61" r:id="rId40" xr:uid="{7DC12D53-CADF-41F0-84FA-EC3FEF8D2B09}"/>
+    <hyperlink ref="E62" r:id="rId41" xr:uid="{E6D5499C-381E-4F21-AC15-85498A547D9F}"/>
+    <hyperlink ref="E63" r:id="rId42" xr:uid="{23D43F97-F3BD-4B09-B054-21598B4266EC}"/>
+    <hyperlink ref="E65" r:id="rId43" xr:uid="{17E1119E-5558-4FBE-8345-09B1C036E379}"/>
+    <hyperlink ref="E66" r:id="rId44" xr:uid="{6C304B39-61E6-4B75-9A64-ECE8CBB3A738}"/>
+    <hyperlink ref="E67" r:id="rId45" xr:uid="{BE0F3DB2-2E1A-4DB0-94E3-DFA902B71F20}"/>
   </hyperlinks>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup orientation="portrait" r:id="rId46"/>

--- a/doc/001_OpenVLSI_Resource.xlsx
+++ b/doc/001_OpenVLSI_Resource.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\Git\VLSIT_SOC_Starter\doc\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{F243152B-6ECF-4FF6-B003-3A0D6A01743E}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{17533920-8E06-4338-8E94-55BA3526306E}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="13896" activeTab="1" xr2:uid="{B6857A90-25D4-4A67-8903-7C0067D27823}"/>
   </bookViews>
@@ -36,7 +36,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="107" uniqueCount="95">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="110" uniqueCount="98">
   <si>
     <t>No.</t>
   </si>
@@ -278,59 +278,10 @@
     <t>AXI</t>
   </si>
   <si>
-    <t>https://github.com/ZipCPU/wb2axip/blob/master/README.md</t>
-  </si>
-  <si>
     <t>https://github.com/funningboy/uvm_axi.git</t>
   </si>
   <si>
     <t>https://github.com/Architech-Silica/Designing-a-Custom-AXI-Master-using-BFMs.git</t>
-  </si>
-  <si>
-    <r>
-      <rPr>
-        <b/>
-        <sz val="13"/>
-        <color theme="1"/>
-        <rFont val="Arial"/>
-        <family val="2"/>
-      </rPr>
-      <t>Initial guess:</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="13"/>
-        <color theme="1"/>
-        <rFont val="Arial"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve">
-Last updated 2013 --&gt; It may become outdated.
-Maybe AXI3 (WID exsits)</t>
-    </r>
-  </si>
-  <si>
-    <r>
-      <rPr>
-        <b/>
-        <sz val="13"/>
-        <color theme="1"/>
-        <rFont val="Arial"/>
-        <family val="2"/>
-      </rPr>
-      <t>Initial guess:</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="13"/>
-        <color theme="1"/>
-        <rFont val="Arial"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve">
-Maybe AXI3 (WID exsits)
-AXI master only </t>
-    </r>
   </si>
   <si>
     <t>AHB</t>
@@ -767,23 +718,261 @@
 Tool generate</t>
   </si>
   <si>
-    <t xml:space="preserve">per README
-"The bridge does not implementAXI ID" and "Support FIXED/ INCR/ WRAP" -- &gt; Most likely AXI4
+    <t>x</t>
+  </si>
+  <si>
+    <t>No handling for unaligned addresses yet. May fail on AXI unaligned transfers.</t>
+  </si>
+  <si>
+    <t>true AXI multiple outstanding transaction
+out-of-order completion
+concurrent backend execution</t>
+  </si>
+  <si>
+    <r>
+      <t>per README
+"The bridge does not implementAXI ID" and "Support FIXED/ INCR/ WRAP" -- &gt; Most likely AXI4.</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="13"/>
+        <color rgb="FFFF0000"/>
+        <rFont val="Arial"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve"> However AxLEN is only 4 bits (16 bytes) instead of 5 bits (256 bytes).</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="13"/>
+        <color theme="1"/>
+        <rFont val="Arial"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">
 AHB-lite 
 The bitwidth parameter defaults to 32 both Address and Data
 Features:
-Exist FIFO
+Exist FIFO for AW, W, AR, R
+Brust support FIXED, INCR, WRAP
+Support narrow transfer
+      aligned narrow transfer → OKAY
+      illegal unaligned narrow transfer → SLVERR
 </t>
-  </si>
-  <si>
-    <t>x</t>
+    </r>
+    <r>
+      <rPr>
+        <i/>
+        <sz val="13"/>
+        <color theme="1"/>
+        <rFont val="Arial"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">Note
+</t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <i/>
+        <sz val="13"/>
+        <color rgb="FF0070C0"/>
+        <rFont val="Arial"/>
+        <family val="2"/>
+      </rPr>
+      <t>Outstanding transactions</t>
+    </r>
+    <r>
+      <rPr>
+        <i/>
+        <sz val="13"/>
+        <color rgb="FF0070C0"/>
+        <rFont val="Arial"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve"> and </t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <i/>
+        <sz val="13"/>
+        <color rgb="FF0070C0"/>
+        <rFont val="Arial"/>
+        <family val="2"/>
+      </rPr>
+      <t>out-of-order</t>
+    </r>
+    <r>
+      <rPr>
+        <i/>
+        <sz val="13"/>
+        <color rgb="FF0070C0"/>
+        <rFont val="Arial"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve"> are not supported since AWID, ARID, RID, and BID are not found at the top level
+Unsupport unalign access.</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="13"/>
+        <color rgb="FF0070C0"/>
+        <rFont val="Arial"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">
+</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="13"/>
+        <color theme="1"/>
+        <rFont val="Arial"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">
+</t>
+    </r>
+  </si>
+  <si>
+    <t>https://github.com/ZipCPU/wb2axip.git</t>
+  </si>
+  <si>
+    <t>High-performance AXI/Wishbone/APB interconnect ecosystem
+AXI4 full protocol support
+AXI4-Lite protocol support
+AXI-Stream protocol support
+Fully pipelined AXI architecture
+Multiple outstanding AXI transactions support
+Sustained 100% throughput design (up to 1 transaction per cycle)
+Simultaneous AXI read/write channel operation
+AXI burst transaction support
+AXI ID handling and transaction routing support
+AXI backpressure handling with VALID/READY decoupling
+Extensive skid-buffer based pipeline optimization
+Includes a complete high-performance AXI infrastructure ecosystem featuring AXI/AXI-Lite crossbars, protocol bridges, DMA engines, AXI-Stream components, CDC modules, bus firewalls, performance monitors, and formally verified master/slave reference designs optimized for fully pipelined 100% throughput operation.
+Full AXI crossbar (AXIXBAR) with NxM topology
+AXI-Lite crossbar (AXILXBAR) with concurrent master/slave connections
+Support for multiple active AXI channel connections simultaneously
+Arbitration and starvation detection inside AXI interconnect
+Optional low-power AXI channel optimization
+AXI channel linger optimization to reduce reopen latency
+AXI4 ↔ AXI-Lite bridge (AXI2AXILITE)
+AXI3 ↔ AXI4 bridge support (AXI32AXI)
+AXI ↔ Wishbone bridge support
+AXI-Lite ↔ Wishbone bridge support
+AXI-Lite ↔ APB bridge support (AXIL2APB)
+AXI firewall / fault isolator (AXISAFETY)
+AXI-Lite firewall / fault isolator (AXILSAFETY)
+AXI protocol violation detection and timeout protection
+Optional automatic slave reset/recovery after AXI fault detection
+AXI clock domain crossing support (AXIXCLK)
+AXI asynchronous FIFO based CDC implementation
+AXI performance monitor/profiler (AXIPERF)
+AXI-based DMA engines:
+Memory-to-memory DMA
+Stream-to-memory DMA
+Memory-to-stream DMA
+Scatter-gather DMA
+AXI stream infrastructure:
+Broadcast
+Switch/router
+Stream packing
+Stream random generator
+AXI video/framebuffer support (AXIVCAMERA, AXIVDISPLAY)
+AXI virtual FIFO support (AXIVFIFO)
+Formally verified AXI/AXI-Lite protocol properties
+Formal verification applied to many AXI cores and interconnect components</t>
+  </si>
+  <si>
+    <t xml:space="preserve">For Verify </t>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="13"/>
+        <color theme="1"/>
+        <rFont val="Arial"/>
+        <family val="2"/>
+      </rPr>
+      <t>Initial guess:</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="13"/>
+        <color theme="1"/>
+        <rFont val="Arial"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">
+Maybe AXI3 (WID exsits)
+AXI master only 
+----
+Custom AXI4 Master IP implementation
+Supports AXI4 burst transactions (up to 256 beats)
+Supports both</t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="13"/>
+        <color theme="1"/>
+        <rFont val="Arial"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve"> 32-bit </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="13"/>
+        <color theme="1"/>
+        <rFont val="Arial"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">and </t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="13"/>
+        <color theme="1"/>
+        <rFont val="Arial"/>
+        <family val="2"/>
+      </rPr>
+      <t>64-bit data widths/ 32-bit address</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="13"/>
+        <color theme="1"/>
+        <rFont val="Arial"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">
+Modular implementation of all five AXI4 channels:
+Write Address (AW)
+Write Data (W)
+Write Response (B)
+Read Address (AR)
+Read Data (R)
+Bus Functional Model (BFM)-based verification environment
+Individual testbenches for each AXI4 channel
+Full-system simulation testbench support
+Example HDL control interface for AXI master operation
+Example C software for triggering AXI transactions from Cortex-A9
+Designed for Xilinx Vivado and Zynq-7000 platforms
+Compatible with AXI4 interconnect-based embedded systems
+Fully commented reference source code for learning and customization</t>
+    </r>
   </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
-  <fonts count="9" x14ac:knownFonts="1">
+  <fonts count="13" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -846,6 +1035,33 @@
       <u/>
       <sz val="13"/>
       <color theme="1"/>
+      <name val="Arial"/>
+      <family val="2"/>
+    </font>
+    <font>
+      <sz val="13"/>
+      <color rgb="FFFF0000"/>
+      <name val="Arial"/>
+      <family val="2"/>
+    </font>
+    <font>
+      <i/>
+      <sz val="13"/>
+      <color rgb="FF0070C0"/>
+      <name val="Arial"/>
+      <family val="2"/>
+    </font>
+    <font>
+      <sz val="13"/>
+      <color rgb="FF0070C0"/>
+      <name val="Arial"/>
+      <family val="2"/>
+    </font>
+    <font>
+      <b/>
+      <i/>
+      <sz val="13"/>
+      <color rgb="FF0070C0"/>
       <name val="Arial"/>
       <family val="2"/>
     </font>
@@ -1393,7 +1609,7 @@
         <v>5</v>
       </c>
       <c r="C6" s="1" t="s">
-        <v>94</v>
+        <v>90</v>
       </c>
       <c r="D6" s="1" t="s">
         <v>17</v>
@@ -1411,43 +1627,45 @@
         <v>40</v>
       </c>
       <c r="F7" s="1"/>
-      <c r="G7" s="1"/>
-    </row>
-    <row r="8" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="G7" s="4"/>
+    </row>
+    <row r="8" spans="1:7" ht="409.6" x14ac:dyDescent="0.3">
       <c r="A8" s="1"/>
       <c r="B8" s="1"/>
       <c r="C8" s="1"/>
       <c r="D8" s="1"/>
-      <c r="E8" s="3" t="s">
-        <v>41</v>
+      <c r="E8" s="8" t="s">
+        <v>94</v>
       </c>
       <c r="F8" s="1"/>
-      <c r="G8" s="1"/>
-    </row>
-    <row r="9" spans="1:7" ht="50.4" x14ac:dyDescent="0.3">
+      <c r="G8" s="4" t="s">
+        <v>95</v>
+      </c>
+    </row>
+    <row r="9" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A9" s="1"/>
       <c r="B9" s="1"/>
       <c r="C9" s="1"/>
       <c r="D9" s="1"/>
       <c r="E9" s="8" t="s">
-        <v>42</v>
+        <v>41</v>
       </c>
       <c r="F9" s="1"/>
       <c r="G9" s="4" t="s">
-        <v>44</v>
-      </c>
-    </row>
-    <row r="10" spans="1:7" ht="50.4" x14ac:dyDescent="0.3">
+        <v>96</v>
+      </c>
+    </row>
+    <row r="10" spans="1:7" ht="352.8" x14ac:dyDescent="0.3">
       <c r="A10" s="1"/>
       <c r="B10" s="1"/>
       <c r="C10" s="1"/>
       <c r="D10" s="1"/>
       <c r="E10" s="8" t="s">
-        <v>43</v>
+        <v>42</v>
       </c>
       <c r="F10" s="1"/>
       <c r="G10" s="4" t="s">
-        <v>45</v>
+        <v>97</v>
       </c>
     </row>
     <row r="11" spans="1:7" x14ac:dyDescent="0.3">
@@ -1456,7 +1674,7 @@
       <c r="C11" s="1"/>
       <c r="D11" s="1"/>
       <c r="E11" s="8" t="s">
-        <v>46</v>
+        <v>43</v>
       </c>
       <c r="F11" s="1"/>
       <c r="G11" s="4"/>
@@ -1467,11 +1685,11 @@
       <c r="C12" s="1"/>
       <c r="D12" s="1"/>
       <c r="E12" s="8" t="s">
-        <v>47</v>
+        <v>44</v>
       </c>
       <c r="F12" s="1"/>
       <c r="G12" s="10" t="s">
-        <v>48</v>
+        <v>45</v>
       </c>
     </row>
     <row r="13" spans="1:7" ht="67.2" x14ac:dyDescent="0.3">
@@ -1480,11 +1698,11 @@
       <c r="C13" s="1"/>
       <c r="D13" s="1"/>
       <c r="E13" s="8" t="s">
-        <v>49</v>
+        <v>46</v>
       </c>
       <c r="F13" s="1"/>
       <c r="G13" s="4" t="s">
-        <v>51</v>
+        <v>48</v>
       </c>
     </row>
     <row r="14" spans="1:7" ht="33.6" x14ac:dyDescent="0.3">
@@ -1493,11 +1711,11 @@
       <c r="C14" s="1"/>
       <c r="D14" s="1"/>
       <c r="E14" s="8" t="s">
-        <v>50</v>
+        <v>47</v>
       </c>
       <c r="F14" s="1"/>
       <c r="G14" s="4" t="s">
-        <v>52</v>
+        <v>49</v>
       </c>
     </row>
     <row r="15" spans="1:7" x14ac:dyDescent="0.3">
@@ -1506,7 +1724,7 @@
       <c r="C15" s="1"/>
       <c r="D15" s="1"/>
       <c r="E15" s="8" t="s">
-        <v>53</v>
+        <v>50</v>
       </c>
       <c r="F15" s="1"/>
       <c r="G15" s="4"/>
@@ -1517,11 +1735,11 @@
       <c r="C16" s="1"/>
       <c r="D16" s="1"/>
       <c r="E16" s="8" t="s">
-        <v>54</v>
+        <v>51</v>
       </c>
       <c r="F16" s="1"/>
       <c r="G16" s="4" t="s">
-        <v>55</v>
+        <v>52</v>
       </c>
     </row>
     <row r="17" spans="1:13" x14ac:dyDescent="0.3">
@@ -1530,7 +1748,7 @@
       <c r="C17" s="1"/>
       <c r="D17" s="1"/>
       <c r="E17" s="8" t="s">
-        <v>56</v>
+        <v>53</v>
       </c>
       <c r="F17" s="1"/>
       <c r="G17" s="4"/>
@@ -1541,11 +1759,11 @@
       <c r="C18" s="1"/>
       <c r="D18" s="1"/>
       <c r="E18" s="8" t="s">
-        <v>58</v>
+        <v>55</v>
       </c>
       <c r="F18" s="1"/>
       <c r="G18" s="4" t="s">
-        <v>59</v>
+        <v>56</v>
       </c>
     </row>
     <row r="19" spans="1:13" ht="409.6" x14ac:dyDescent="0.3">
@@ -1556,7 +1774,7 @@
         <v>24</v>
       </c>
       <c r="C19" s="1" t="s">
-        <v>94</v>
+        <v>90</v>
       </c>
       <c r="D19" s="1"/>
       <c r="E19" s="9" t="s">
@@ -1610,14 +1828,17 @@
         <v>25</v>
       </c>
       <c r="C21" s="1" t="s">
-        <v>94</v>
+        <v>90</v>
       </c>
       <c r="D21" s="1"/>
       <c r="E21" s="8" t="s">
-        <v>60</v>
+        <v>57</v>
       </c>
       <c r="F21" s="1"/>
       <c r="G21" s="4" t="s">
+        <v>88</v>
+      </c>
+      <c r="H21" s="2" t="s">
         <v>91</v>
       </c>
     </row>
@@ -1627,25 +1848,28 @@
       <c r="C22" s="1"/>
       <c r="D22" s="1"/>
       <c r="E22" s="8" t="s">
-        <v>61</v>
+        <v>58</v>
       </c>
       <c r="F22" s="1"/>
       <c r="G22" s="12" t="s">
-        <v>92</v>
-      </c>
-    </row>
-    <row r="23" spans="1:13" ht="134.4" x14ac:dyDescent="0.3">
+        <v>89</v>
+      </c>
+    </row>
+    <row r="23" spans="1:13" ht="304.8" x14ac:dyDescent="0.3">
       <c r="A23" s="1"/>
       <c r="B23" s="1"/>
       <c r="C23" s="1"/>
       <c r="D23" s="1"/>
       <c r="E23" s="8" t="s">
-        <v>62</v>
+        <v>59</v>
       </c>
       <c r="F23" s="1"/>
       <c r="G23" s="4" t="s">
         <v>93</v>
       </c>
+      <c r="H23" s="7" t="s">
+        <v>92</v>
+      </c>
     </row>
     <row r="24" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A24" s="1">
@@ -1655,7 +1879,7 @@
         <v>26</v>
       </c>
       <c r="C24" s="1" t="s">
-        <v>94</v>
+        <v>90</v>
       </c>
       <c r="D24" s="1"/>
       <c r="E24" s="8"/>
@@ -1668,7 +1892,7 @@
       <c r="C25" s="1"/>
       <c r="D25" s="1"/>
       <c r="E25" s="11" t="s">
-        <v>57</v>
+        <v>54</v>
       </c>
       <c r="F25" s="1"/>
       <c r="G25" s="1"/>
@@ -1679,7 +1903,7 @@
       <c r="C26" s="1"/>
       <c r="D26" s="1"/>
       <c r="E26" s="8" t="s">
-        <v>63</v>
+        <v>60</v>
       </c>
       <c r="F26" s="1"/>
       <c r="G26" s="1"/>
@@ -1690,7 +1914,7 @@
       <c r="C27" s="1"/>
       <c r="D27" s="1"/>
       <c r="E27" s="11" t="s">
-        <v>64</v>
+        <v>61</v>
       </c>
       <c r="F27" s="1"/>
       <c r="G27" s="1"/>
@@ -1703,7 +1927,7 @@
         <v>27</v>
       </c>
       <c r="C28" s="1" t="s">
-        <v>94</v>
+        <v>90</v>
       </c>
       <c r="D28" s="1"/>
       <c r="E28" s="3"/>
@@ -1716,7 +1940,7 @@
       <c r="C29" s="1"/>
       <c r="D29" s="1"/>
       <c r="E29" s="8" t="s">
-        <v>65</v>
+        <v>62</v>
       </c>
       <c r="F29" s="1"/>
       <c r="G29" s="1"/>
@@ -1727,7 +1951,7 @@
       <c r="C30" s="1"/>
       <c r="D30" s="1"/>
       <c r="E30" s="8" t="s">
-        <v>66</v>
+        <v>63</v>
       </c>
       <c r="F30" s="1"/>
       <c r="G30" s="1"/>
@@ -1738,7 +1962,7 @@
       <c r="C31" s="1"/>
       <c r="D31" s="1"/>
       <c r="E31" s="8" t="s">
-        <v>67</v>
+        <v>64</v>
       </c>
       <c r="F31" s="1"/>
       <c r="G31" s="1"/>
@@ -1804,7 +2028,7 @@
       <c r="C37" s="1"/>
       <c r="D37" s="1"/>
       <c r="E37" s="8" t="s">
-        <v>68</v>
+        <v>65</v>
       </c>
       <c r="F37" s="1"/>
       <c r="G37" s="4"/>
@@ -1815,7 +2039,7 @@
       <c r="C38" s="1"/>
       <c r="D38" s="1"/>
       <c r="E38" s="8" t="s">
-        <v>68</v>
+        <v>65</v>
       </c>
       <c r="F38" s="1"/>
       <c r="G38" s="4"/>
@@ -1826,7 +2050,7 @@
       <c r="C39" s="1"/>
       <c r="D39" s="1"/>
       <c r="E39" s="8" t="s">
-        <v>69</v>
+        <v>66</v>
       </c>
       <c r="F39" s="1"/>
       <c r="G39" s="4"/>
@@ -1850,7 +2074,7 @@
       <c r="C41" s="1"/>
       <c r="D41" s="1"/>
       <c r="E41" s="8" t="s">
-        <v>70</v>
+        <v>67</v>
       </c>
       <c r="F41" s="1"/>
       <c r="G41" s="1"/>
@@ -1861,7 +2085,7 @@
       <c r="C42" s="1"/>
       <c r="D42" s="1"/>
       <c r="E42" s="11" t="s">
-        <v>71</v>
+        <v>68</v>
       </c>
       <c r="F42" s="1"/>
       <c r="G42" s="1"/>
@@ -1872,7 +2096,7 @@
       <c r="C43" s="1"/>
       <c r="D43" s="1"/>
       <c r="E43" s="8" t="s">
-        <v>72</v>
+        <v>69</v>
       </c>
       <c r="F43" s="1"/>
       <c r="G43" s="1"/>
@@ -1885,7 +2109,7 @@
         <v>7</v>
       </c>
       <c r="C44" s="1" t="s">
-        <v>94</v>
+        <v>90</v>
       </c>
       <c r="D44" s="1"/>
       <c r="E44" s="3"/>
@@ -1898,7 +2122,7 @@
       <c r="C45" s="1"/>
       <c r="D45" s="1"/>
       <c r="E45" s="8" t="s">
-        <v>73</v>
+        <v>70</v>
       </c>
       <c r="F45" s="1"/>
       <c r="G45" s="1"/>
@@ -1909,7 +2133,7 @@
       <c r="C46" s="1"/>
       <c r="D46" s="1"/>
       <c r="E46" s="8" t="s">
-        <v>74</v>
+        <v>71</v>
       </c>
       <c r="F46" s="1"/>
       <c r="G46" s="1"/>
@@ -1920,7 +2144,7 @@
       <c r="C47" s="1"/>
       <c r="D47" s="1"/>
       <c r="E47" s="8" t="s">
-        <v>75</v>
+        <v>72</v>
       </c>
       <c r="F47" s="1"/>
       <c r="G47" s="1"/>
@@ -1933,7 +2157,7 @@
         <v>21</v>
       </c>
       <c r="C48" s="1" t="s">
-        <v>94</v>
+        <v>90</v>
       </c>
       <c r="D48" s="1"/>
       <c r="E48" s="3"/>
@@ -1946,7 +2170,7 @@
       <c r="C49" s="1"/>
       <c r="D49" s="1"/>
       <c r="E49" s="8" t="s">
-        <v>76</v>
+        <v>73</v>
       </c>
       <c r="F49" s="1"/>
       <c r="G49" s="1"/>
@@ -1957,7 +2181,7 @@
       <c r="C50" s="1"/>
       <c r="D50" s="1"/>
       <c r="E50" s="8" t="s">
-        <v>77</v>
+        <v>74</v>
       </c>
       <c r="F50" s="1"/>
       <c r="G50" s="1"/>
@@ -1968,7 +2192,7 @@
       <c r="C51" s="1"/>
       <c r="D51" s="1"/>
       <c r="E51" s="8" t="s">
-        <v>78</v>
+        <v>75</v>
       </c>
       <c r="F51" s="1"/>
       <c r="G51" s="1"/>
@@ -1981,7 +2205,7 @@
         <v>8</v>
       </c>
       <c r="C52" s="1" t="s">
-        <v>94</v>
+        <v>90</v>
       </c>
       <c r="D52" s="1"/>
       <c r="E52" s="1"/>
@@ -1994,7 +2218,7 @@
       <c r="C53" s="1"/>
       <c r="D53" s="1"/>
       <c r="E53" s="8" t="s">
-        <v>79</v>
+        <v>76</v>
       </c>
       <c r="F53" s="1"/>
       <c r="G53" s="1"/>
@@ -2005,7 +2229,7 @@
       <c r="C54" s="1"/>
       <c r="D54" s="1"/>
       <c r="E54" s="9" t="s">
-        <v>80</v>
+        <v>77</v>
       </c>
       <c r="F54" s="1"/>
       <c r="G54" s="1"/>
@@ -2016,7 +2240,7 @@
       <c r="C55" s="1"/>
       <c r="D55" s="1"/>
       <c r="E55" s="8" t="s">
-        <v>81</v>
+        <v>78</v>
       </c>
       <c r="F55" s="1"/>
       <c r="G55" s="1"/>
@@ -2029,7 +2253,7 @@
         <v>9</v>
       </c>
       <c r="C56" s="1" t="s">
-        <v>94</v>
+        <v>90</v>
       </c>
       <c r="D56" s="1"/>
       <c r="E56" s="1"/>
@@ -2042,7 +2266,7 @@
       <c r="C57" s="1"/>
       <c r="D57" s="1"/>
       <c r="E57" s="8" t="s">
-        <v>82</v>
+        <v>79</v>
       </c>
       <c r="F57" s="1"/>
       <c r="G57" s="1"/>
@@ -2053,7 +2277,7 @@
       <c r="C58" s="1"/>
       <c r="D58" s="1"/>
       <c r="E58" s="8" t="s">
-        <v>83</v>
+        <v>80</v>
       </c>
       <c r="F58" s="1"/>
       <c r="G58" s="1"/>
@@ -2064,7 +2288,7 @@
       <c r="C59" s="1"/>
       <c r="D59" s="1"/>
       <c r="E59" s="8" t="s">
-        <v>84</v>
+        <v>81</v>
       </c>
       <c r="F59" s="1"/>
       <c r="G59" s="1"/>
@@ -2077,7 +2301,7 @@
         <v>10</v>
       </c>
       <c r="C60" s="1" t="s">
-        <v>94</v>
+        <v>90</v>
       </c>
       <c r="D60" s="1"/>
       <c r="E60" s="1"/>
@@ -2090,7 +2314,7 @@
       <c r="C61" s="1"/>
       <c r="D61" s="1"/>
       <c r="E61" s="8" t="s">
-        <v>85</v>
+        <v>82</v>
       </c>
       <c r="F61" s="1"/>
       <c r="G61" s="1"/>
@@ -2101,7 +2325,7 @@
       <c r="C62" s="1"/>
       <c r="D62" s="1"/>
       <c r="E62" s="8" t="s">
-        <v>86</v>
+        <v>83</v>
       </c>
       <c r="F62" s="1"/>
       <c r="G62" s="1"/>
@@ -2112,7 +2336,7 @@
       <c r="C63" s="1"/>
       <c r="D63" s="1"/>
       <c r="E63" s="8" t="s">
-        <v>87</v>
+        <v>84</v>
       </c>
       <c r="F63" s="1"/>
       <c r="G63" s="1"/>
@@ -2125,7 +2349,7 @@
         <v>11</v>
       </c>
       <c r="C64" s="1" t="s">
-        <v>94</v>
+        <v>90</v>
       </c>
       <c r="D64" s="1"/>
       <c r="F64" s="1"/>
@@ -2137,7 +2361,7 @@
       <c r="C65" s="1"/>
       <c r="D65" s="1"/>
       <c r="E65" s="8" t="s">
-        <v>88</v>
+        <v>85</v>
       </c>
       <c r="F65" s="1"/>
       <c r="G65" s="1"/>
@@ -2148,7 +2372,7 @@
       <c r="C66" s="1"/>
       <c r="D66" s="1"/>
       <c r="E66" s="8" t="s">
-        <v>89</v>
+        <v>86</v>
       </c>
       <c r="F66" s="1"/>
       <c r="G66" s="1"/>
@@ -2159,7 +2383,7 @@
       <c r="C67" s="1"/>
       <c r="D67" s="1"/>
       <c r="E67" s="8" t="s">
-        <v>90</v>
+        <v>87</v>
       </c>
       <c r="F67" s="1"/>
       <c r="G67" s="1"/>
@@ -2211,8 +2435,9 @@
     <hyperlink ref="E65" r:id="rId43" xr:uid="{17E1119E-5558-4FBE-8345-09B1C036E379}"/>
     <hyperlink ref="E66" r:id="rId44" xr:uid="{6C304B39-61E6-4B75-9A64-ECE8CBB3A738}"/>
     <hyperlink ref="E67" r:id="rId45" xr:uid="{BE0F3DB2-2E1A-4DB0-94E3-DFA902B71F20}"/>
+    <hyperlink ref="E8" r:id="rId46" xr:uid="{C3DD15BC-C921-43F1-9AC0-E531C3BCBB42}"/>
   </hyperlinks>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
-  <pageSetup orientation="portrait" r:id="rId46"/>
+  <pageSetup orientation="portrait" r:id="rId47"/>
 </worksheet>
 </file>